--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -13,54 +13,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53" uniqueCount="31">
-  <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-04 21:46)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
+  <si>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 10:24)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-04 21:46</t>
+    <t>2026-10-05 10:24</t>
   </si>
   <si>
     <t>Iteration</t>
   </si>
   <si>
-    <t>Grid 1/12</t>
-  </si>
-  <si>
-    <t>Grid 2/12</t>
-  </si>
-  <si>
-    <t>Grid 3/12</t>
-  </si>
-  <si>
-    <t>Grid 4/12</t>
-  </si>
-  <si>
-    <t>Grid 5/12</t>
-  </si>
-  <si>
-    <t>Grid 6/12</t>
-  </si>
-  <si>
-    <t>Grid 7/12</t>
-  </si>
-  <si>
-    <t>Grid 8/12</t>
-  </si>
-  <si>
-    <t>Grid 9/12</t>
-  </si>
-  <si>
-    <t>Grid 10/12</t>
-  </si>
-  <si>
-    <t>Grid 11/12</t>
-  </si>
-  <si>
-    <t>Grid 12/12</t>
+    <t>Grid 1/16</t>
+  </si>
+  <si>
+    <t>Grid 2/16</t>
+  </si>
+  <si>
+    <t>Grid 3/16</t>
+  </si>
+  <si>
+    <t>Grid 4/16</t>
+  </si>
+  <si>
+    <t>Grid 5/16</t>
+  </si>
+  <si>
+    <t>Grid 6/16</t>
+  </si>
+  <si>
+    <t>Grid 7/16</t>
+  </si>
+  <si>
+    <t>Grid 8/16</t>
+  </si>
+  <si>
+    <t>Grid 9/16</t>
+  </si>
+  <si>
+    <t>Grid 10/16</t>
+  </si>
+  <si>
+    <t>Grid 11/16</t>
+  </si>
+  <si>
+    <t>Grid 12/16</t>
+  </si>
+  <si>
+    <t>Grid 13/16</t>
+  </si>
+  <si>
+    <t>Grid 14/16</t>
+  </si>
+  <si>
+    <t>Grid 15/16</t>
+  </si>
+  <si>
+    <t>Grid 16/16</t>
   </si>
   <si>
     <t>W_pay_kg</t>
@@ -106,6 +118,9 @@
   </si>
   <si>
     <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -151,17 +166,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="57.44140625" customWidth="true"/>
     <col min="2" max="2" width="9.5546875" customWidth="true"/>
     <col min="3" max="3" width="12.5546875" customWidth="true"/>
-    <col min="4" max="4" width="12.5546875" customWidth="true"/>
+    <col min="4" max="4" width="11.5546875" customWidth="true"/>
     <col min="5" max="5" width="11.5546875" customWidth="true"/>
     <col min="6" max="6" width="11.5546875" customWidth="true"/>
     <col min="7" max="7" width="13.33203125" customWidth="true"/>
-    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="8" max="8" width="11.5546875" customWidth="true"/>
     <col min="9" max="9" width="12.5546875" customWidth="true"/>
     <col min="10" max="10" width="11.5546875" customWidth="true"/>
     <col min="11" max="11" width="12.77734375" customWidth="true"/>
@@ -200,46 +215,46 @@
         <v>3</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -250,46 +265,46 @@
         <v>4</v>
       </c>
       <c r="C3" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.02</v>
       </c>
       <c r="D3" s="0">
-        <v>0.46558692340518659</v>
+        <v>4.0782797892058778</v>
       </c>
       <c r="E3" s="0">
-        <v>1.4724131143967178</v>
+        <v>12.265416257645498</v>
       </c>
       <c r="F3" s="0">
-        <v>10.418250858810969</v>
+        <v>9.8282748649767111</v>
       </c>
       <c r="G3" s="0">
-        <v>65.890168177656093</v>
+        <v>5.6878030273343256</v>
       </c>
       <c r="H3" s="0">
-        <v>0.45530313292132785</v>
+        <v>5.2744442548074577</v>
       </c>
       <c r="I3" s="0">
-        <v>0.77510809392222291</v>
+        <v>0.68980643032778466</v>
       </c>
       <c r="J3" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>36.209101634183377</v>
+        <v>120.17772092426242</v>
       </c>
       <c r="L3" s="0">
         <v>600</v>
       </c>
       <c r="M3" s="0">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N3" s="0">
         <v>600</v>
       </c>
       <c r="O3" s="0">
-        <v>42.968077583206139</v>
+        <v>42.931378255005832</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -300,46 +315,46 @@
         <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>0.11410367420435331</v>
+        <v>0.225783489151373</v>
       </c>
       <c r="D4" s="0">
-        <v>0.96379557833242158</v>
+        <v>4.2840632783572508</v>
       </c>
       <c r="E4" s="0">
-        <v>2.879507001925028</v>
+        <v>13.724994100341393</v>
       </c>
       <c r="F4" s="0">
-        <v>10.416670998550122</v>
+        <v>10.073182996903961</v>
       </c>
       <c r="G4" s="0">
-        <v>30.962328992460101</v>
+        <v>5.3539603015768265</v>
       </c>
       <c r="H4" s="0">
-        <v>0.96891936027504755</v>
+        <v>5.6033288089873441</v>
       </c>
       <c r="I4" s="0">
-        <v>0.77487303150271325</v>
+        <v>0.72461296185796842</v>
       </c>
       <c r="J4" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>37.25824027953928</v>
+        <v>127.13542137442248</v>
       </c>
       <c r="L4" s="0">
         <v>600</v>
       </c>
       <c r="M4" s="0">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N4" s="0">
         <v>600</v>
       </c>
       <c r="O4" s="0">
-        <v>42.951037436646317</v>
+        <v>42.952385342180236</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -350,46 +365,46 @@
         <v>6</v>
       </c>
       <c r="C5" s="0">
-        <v>0.17820734840870661</v>
+        <v>0.43156697830274604</v>
       </c>
       <c r="D5" s="0">
-        <v>1.4653379681117464</v>
+        <v>4.4898467675086238</v>
       </c>
       <c r="E5" s="0">
-        <v>4.3648868247180772</v>
+        <v>15.198030002843097</v>
       </c>
       <c r="F5" s="0">
-        <v>10.414999101027771</v>
+        <v>10.312276400324862</v>
       </c>
       <c r="G5" s="0">
-        <v>19.737192757953572</v>
+        <v>5.0482712875213078</v>
       </c>
       <c r="H5" s="0">
-        <v>1.519972995547241</v>
+        <v>5.9426283357941223</v>
       </c>
       <c r="I5" s="0">
-        <v>0.77462431397370846</v>
+        <v>0.75941949338815185</v>
       </c>
       <c r="J5" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>43.996211225921343</v>
+        <v>134.41831511139935</v>
       </c>
       <c r="L5" s="0">
         <v>600</v>
       </c>
       <c r="M5" s="0">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N5" s="0">
         <v>600</v>
       </c>
       <c r="O5" s="0">
-        <v>42.948373434689202</v>
+        <v>42.969426477571155</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -400,46 +415,46 @@
         <v>7</v>
       </c>
       <c r="C6" s="0">
-        <v>0.24231102261305998</v>
+        <v>0.63735046745411894</v>
       </c>
       <c r="D6" s="0">
-        <v>1.966999218035945</v>
+        <v>4.6956302566599968</v>
       </c>
       <c r="E6" s="0">
-        <v>5.9348546363466941</v>
+        <v>16.797229211998935</v>
       </c>
       <c r="F6" s="0">
-        <v>10.410917786021505</v>
+        <v>10.545950569971355</v>
       </c>
       <c r="G6" s="0">
-        <v>14.246865607119565</v>
+        <v>4.7670589433933594</v>
       </c>
       <c r="H6" s="0">
-        <v>2.1057263279726697</v>
+        <v>6.2931883906274821</v>
       </c>
       <c r="I6" s="0">
-        <v>0.77401733045655718</v>
+        <v>0.79422602491833561</v>
       </c>
       <c r="J6" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>52.498953267962236</v>
+        <v>142.026402135193</v>
       </c>
       <c r="L6" s="0">
         <v>600</v>
       </c>
       <c r="M6" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N6" s="0">
         <v>600</v>
       </c>
       <c r="O6" s="0">
-        <v>42.949977775555787</v>
+        <v>42.984319308042402</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -450,46 +465,46 @@
         <v>8</v>
       </c>
       <c r="C7" s="0">
-        <v>0.30641469681741324</v>
+        <v>0.84313395660549206</v>
       </c>
       <c r="D7" s="0">
-        <v>2.4690819207619943</v>
+        <v>4.9014137458113698</v>
       </c>
       <c r="E7" s="0">
-        <v>7.4763042040107859</v>
+        <v>18.407660459232378</v>
       </c>
       <c r="F7" s="0">
-        <v>10.412919985340686</v>
+        <v>10.774558101929806</v>
       </c>
       <c r="G7" s="0">
-        <v>10.988980319107812</v>
+        <v>4.5072615194675327</v>
       </c>
       <c r="H7" s="0">
-        <v>2.7300076193453116</v>
+        <v>6.6559261916410968</v>
       </c>
       <c r="I7" s="0">
-        <v>0.77431507288897772</v>
+        <v>0.82903255644851914</v>
       </c>
       <c r="J7" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>62.894369089517646</v>
+        <v>150.40643290956771</v>
       </c>
       <c r="L7" s="0">
         <v>600</v>
       </c>
       <c r="M7" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N7" s="0">
         <v>600</v>
       </c>
       <c r="O7" s="0">
-        <v>42.94797349926219</v>
+        <v>42.995202336864317</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -500,31 +515,31 @@
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <v>0.37051837102176655</v>
+        <v>1.0489174457568651</v>
       </c>
       <c r="D8" s="0">
-        <v>2.9716166716838957</v>
+        <v>5.1071972349627437</v>
       </c>
       <c r="E8" s="0">
-        <v>9.0989024013368649</v>
+        <v>20.147138361395392</v>
       </c>
       <c r="F8" s="0">
-        <v>10.413836416632844</v>
+        <v>10.998414938501062</v>
       </c>
       <c r="G8" s="0">
-        <v>8.8128550005646602</v>
+        <v>4.2663089622887034</v>
       </c>
       <c r="H8" s="0">
-        <v>3.4041181884959904</v>
+        <v>7.0318395280744515</v>
       </c>
       <c r="I8" s="0">
-        <v>0.77445137236879424</v>
+        <v>0.8638390879787029</v>
       </c>
       <c r="J8" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>75.339061362741759</v>
+        <v>159.20367818881724</v>
       </c>
       <c r="L8" s="0">
         <v>600</v>
@@ -536,10 +551,10 @@
         <v>600</v>
       </c>
       <c r="O8" s="0">
-        <v>42.948204130474245</v>
+        <v>43.005879839622558</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -550,46 +565,46 @@
         <v>10</v>
       </c>
       <c r="C9" s="0">
-        <v>0.43462204522611991</v>
+        <v>1.2547009349082379</v>
       </c>
       <c r="D9" s="0">
-        <v>3.4746969160333579</v>
+        <v>5.3129807241141158</v>
       </c>
       <c r="E9" s="0">
-        <v>10.690185053632545</v>
+        <v>22.019371525012144</v>
       </c>
       <c r="F9" s="0">
-        <v>10.414286755685179</v>
+        <v>11.217805490693149</v>
       </c>
       <c r="G9" s="0">
-        <v>7.2425908404501724</v>
+        <v>4.0420279751870716</v>
       </c>
       <c r="H9" s="0">
-        <v>4.1421641317149582</v>
+        <v>7.4220169143217154</v>
       </c>
       <c r="I9" s="0">
-        <v>0.77451835502998145</v>
+        <v>0.89864561950888644</v>
       </c>
       <c r="J9" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>91.204338161356674</v>
+        <v>168.34733192642676</v>
       </c>
       <c r="L9" s="0">
         <v>600</v>
       </c>
       <c r="M9" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N9" s="0">
         <v>600</v>
       </c>
       <c r="O9" s="0">
-        <v>42.946056543042246</v>
+        <v>43.016059103366388</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -600,46 +615,46 @@
         <v>11</v>
       </c>
       <c r="C10" s="0">
-        <v>0.49872571943047322</v>
+        <v>1.4604844240596111</v>
       </c>
       <c r="D10" s="0">
-        <v>3.9784198272006419</v>
+        <v>5.5187642132654897</v>
       </c>
       <c r="E10" s="0">
-        <v>12.358930026875239</v>
+        <v>24.027993990189661</v>
       </c>
       <c r="F10" s="0">
-        <v>10.417618919067657</v>
+        <v>11.432986875467297</v>
       </c>
       <c r="G10" s="0">
-        <v>6.0449598331953398</v>
+        <v>3.8324748357738301</v>
       </c>
       <c r="H10" s="0">
-        <v>4.9628121323913126</v>
+        <v>7.8278400473678733</v>
       </c>
       <c r="I10" s="0">
-        <v>0.77501406532548467</v>
+        <v>0.9334521510390702</v>
       </c>
       <c r="J10" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>110.01048202841855</v>
+        <v>177.83739412239646</v>
       </c>
       <c r="L10" s="0">
         <v>600</v>
       </c>
       <c r="M10" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N10" s="0">
         <v>600</v>
       </c>
       <c r="O10" s="0">
-        <v>42.94531477000303</v>
+        <v>43.024965917964153</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -650,46 +665,46 @@
         <v>12</v>
       </c>
       <c r="C11" s="0">
-        <v>0.56282939363482654</v>
+        <v>1.6662679132109841</v>
       </c>
       <c r="D11" s="0">
-        <v>4.4826766759561343</v>
+        <v>5.7245477024168618</v>
       </c>
       <c r="E11" s="0">
-        <v>14.103210141369969</v>
+        <v>26.176540729946396</v>
       </c>
       <c r="F11" s="0">
-        <v>10.409368105553042</v>
+        <v>11.64419244783379</v>
       </c>
       <c r="G11" s="0">
-        <v>5.0848740227570639</v>
+        <v>3.6361713760615975</v>
       </c>
       <c r="H11" s="0">
-        <v>5.8998511793481434</v>
+        <v>8.2504362136235549</v>
       </c>
       <c r="I11" s="0">
-        <v>0.77378692036366037</v>
+        <v>0.96825868256925363</v>
       </c>
       <c r="J11" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>132.97961006389889</v>
+        <v>187.67386477672636</v>
       </c>
       <c r="L11" s="0">
         <v>600</v>
       </c>
       <c r="M11" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N11" s="0">
         <v>600</v>
       </c>
       <c r="O11" s="0">
-        <v>42.945314078304861</v>
+        <v>43.031336250966703</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -700,46 +715,46 @@
         <v>13</v>
       </c>
       <c r="C12" s="0">
-        <v>0.6269330678391799</v>
+        <v>1.8720514023623571</v>
       </c>
       <c r="D12" s="0">
-        <v>4.9877609367472431</v>
+        <v>5.9303311915682357</v>
       </c>
       <c r="E12" s="0">
-        <v>15.920485581180261</v>
+        <v>28.337621085749401</v>
       </c>
       <c r="F12" s="0">
-        <v>10.414655525931497</v>
+        <v>11.851634766131278</v>
       </c>
       <c r="G12" s="0">
-        <v>4.2923523500272234</v>
+        <v>3.4516349146667103</v>
       </c>
       <c r="H12" s="0">
-        <v>6.9891745955594091</v>
+        <v>8.6915333578658043</v>
       </c>
       <c r="I12" s="0">
-        <v>0.77457320744343183</v>
+        <v>1.0030652140994376</v>
       </c>
       <c r="J12" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>160.27387434938328</v>
+        <v>198.60832196045709</v>
       </c>
       <c r="L12" s="0">
         <v>600</v>
       </c>
       <c r="M12" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N12" s="0">
         <v>600</v>
       </c>
       <c r="O12" s="0">
-        <v>42.945655708162704</v>
+        <v>43.035632453032314</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -750,46 +765,46 @@
         <v>14</v>
       </c>
       <c r="C13" s="0">
-        <v>0.69103674204353316</v>
+        <v>2.0778348915137301</v>
       </c>
       <c r="D13" s="0">
-        <v>5.493510389188109</v>
+        <v>6.1361146807196079</v>
       </c>
       <c r="E13" s="0">
-        <v>17.808506437885175</v>
+        <v>30.640644851482932</v>
       </c>
       <c r="F13" s="0">
-        <v>10.414658483612481</v>
+        <v>12.055508097851106</v>
       </c>
       <c r="G13" s="0">
-        <v>3.6145583141968758</v>
+        <v>3.2778014729258609</v>
       </c>
       <c r="H13" s="0">
-        <v>8.2997692642470877</v>
+        <v>9.152476209372475</v>
       </c>
       <c r="I13" s="0">
-        <v>0.77457364738900003</v>
+        <v>1.0378717456296209</v>
       </c>
       <c r="J13" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>192.55726425794359</v>
+        <v>209.91799351720425</v>
       </c>
       <c r="L13" s="0">
         <v>600</v>
       </c>
       <c r="M13" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N13" s="0">
         <v>600</v>
       </c>
       <c r="O13" s="0">
-        <v>42.946057096896318</v>
+        <v>43.035632453032307</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -800,46 +815,246 @@
         <v>15</v>
       </c>
       <c r="C14" s="0">
-        <v>0.75514041624788653</v>
+        <v>2.2836183806651031</v>
       </c>
       <c r="D14" s="0">
-        <v>5.9999999999964828</v>
+        <v>6.3418981698709818</v>
       </c>
       <c r="E14" s="0">
-        <v>19.764478906289721</v>
+        <v>32.953706077207592</v>
       </c>
       <c r="F14" s="0">
-        <v>10.414641150545249</v>
+        <v>12.255990550132442</v>
       </c>
       <c r="G14" s="0">
-        <v>3.0210169534550344</v>
+        <v>3.1136853363123116</v>
       </c>
       <c r="H14" s="0">
-        <v>9.93043086556996</v>
+        <v>9.634884954537652</v>
       </c>
       <c r="I14" s="0">
-        <v>0.7745710691525739</v>
+        <v>1.0726782771598047</v>
       </c>
       <c r="J14" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>231.43137625800802</v>
+        <v>221.59974778724984</v>
       </c>
       <c r="L14" s="0">
         <v>600</v>
       </c>
       <c r="M14" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N14" s="0">
         <v>600</v>
       </c>
       <c r="O14" s="0">
-        <v>42.946330612334982</v>
+        <v>43.035632453032299</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="0">
+        <v>2.4894018698164757</v>
+      </c>
+      <c r="D15" s="0">
+        <v>6.5476816590223539</v>
+      </c>
+      <c r="E15" s="0">
+        <v>35.547721618663054</v>
+      </c>
+      <c r="F15" s="0">
+        <v>12.453245891433998</v>
+      </c>
+      <c r="G15" s="0">
+        <v>2.9583332474096187</v>
+      </c>
+      <c r="H15" s="0">
+        <v>10.140845364959697</v>
+      </c>
+      <c r="I15" s="0">
+        <v>1.107484808689988</v>
+      </c>
+      <c r="J15" s="0">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="K15" s="0">
+        <v>233.65358477059323</v>
+      </c>
+      <c r="L15" s="0">
+        <v>600</v>
+      </c>
+      <c r="M15" s="0">
+        <v>8</v>
+      </c>
+      <c r="N15" s="0">
+        <v>600</v>
+      </c>
+      <c r="O15" s="0">
+        <v>43.036936113503174</v>
+      </c>
+      <c r="P15" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="0">
+        <v>2.6951853589678492</v>
+      </c>
+      <c r="D16" s="0">
+        <v>6.7534651481737278</v>
+      </c>
+      <c r="E16" s="0">
+        <v>38.153453445181071</v>
+      </c>
+      <c r="F16" s="0">
+        <v>12.647425117394443</v>
+      </c>
+      <c r="G16" s="0">
+        <v>2.8109526881963296</v>
+      </c>
+      <c r="H16" s="0">
+        <v>10.672538220218051</v>
+      </c>
+      <c r="I16" s="0">
+        <v>1.1422913402201718</v>
+      </c>
+      <c r="J16" s="0">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="K16" s="0">
+        <v>246.47290940500514</v>
+      </c>
+      <c r="L16" s="0">
+        <v>600</v>
+      </c>
+      <c r="M16" s="0">
+        <v>7</v>
+      </c>
+      <c r="N16" s="0">
+        <v>600</v>
+      </c>
+      <c r="O16" s="0">
+        <v>43.038213963404566</v>
+      </c>
+      <c r="P16" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="0">
+        <v>2.9009688481192222</v>
+      </c>
+      <c r="D17" s="0">
+        <v>6.9592486373250999</v>
+      </c>
+      <c r="E17" s="0">
+        <v>40.908783653975469</v>
+      </c>
+      <c r="F17" s="0">
+        <v>12.838667803463172</v>
+      </c>
+      <c r="G17" s="0">
+        <v>2.6711156204248723</v>
+      </c>
+      <c r="H17" s="0">
+        <v>11.231262237621952</v>
+      </c>
+      <c r="I17" s="0">
+        <v>1.1770978717503555</v>
+      </c>
+      <c r="J17" s="0">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="K17" s="0">
+        <v>259.94824678259948</v>
+      </c>
+      <c r="L17" s="0">
+        <v>600</v>
+      </c>
+      <c r="M17" s="0">
+        <v>7</v>
+      </c>
+      <c r="N17" s="0">
+        <v>600</v>
+      </c>
+      <c r="O17" s="0">
+        <v>43.038530844657828</v>
+      </c>
+      <c r="P17" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="0">
+        <v>3.1067523372705952</v>
+      </c>
+      <c r="D18" s="0">
+        <v>7.1650321264764738</v>
+      </c>
+      <c r="E18" s="0">
+        <v>43.816424986732407</v>
+      </c>
+      <c r="F18" s="0">
+        <v>13.027103278751726</v>
+      </c>
+      <c r="G18" s="0">
+        <v>2.5380449372512981</v>
+      </c>
+      <c r="H18" s="0">
+        <v>11.820121684878437</v>
+      </c>
+      <c r="I18" s="0">
+        <v>1.2119044032805393</v>
+      </c>
+      <c r="J18" s="0">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="K18" s="0">
+        <v>273.81535937115746</v>
+      </c>
+      <c r="L18" s="0">
+        <v>600</v>
+      </c>
+      <c r="M18" s="0">
+        <v>6</v>
+      </c>
+      <c r="N18" s="0">
+        <v>600</v>
+      </c>
+      <c r="O18" s="0">
+        <v>43.038208225227038</v>
+      </c>
+      <c r="P18" s="0" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 10:24)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 20:19)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-05 10:24</t>
+    <t>2026-10-05 20:19</t>
   </si>
   <si>
     <t>Iteration</t>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 20:19)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 20:27)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-05 20:19</t>
+    <t>2026-10-05 20:27</t>
   </si>
   <si>
     <t>Iteration</t>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 20:27)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 21:45)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-05 20:27</t>
+    <t>2026-10-05 21:45</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -268,40 +268,40 @@
         <v>0.02</v>
       </c>
       <c r="D3" s="0">
-        <v>4.0782797892058778</v>
+        <v>3.5516000000000005</v>
       </c>
       <c r="E3" s="0">
-        <v>12.265416257645498</v>
+        <v>8.7337587366424181</v>
       </c>
       <c r="F3" s="0">
-        <v>9.8282748649767111</v>
+        <v>8.9443583840071384</v>
       </c>
       <c r="G3" s="0">
-        <v>5.6878030273343256</v>
+        <v>6.6442450244202726</v>
       </c>
       <c r="H3" s="0">
-        <v>5.2744442548074577</v>
+        <v>4.5151856817046836</v>
       </c>
       <c r="I3" s="0">
-        <v>0.68980643032778466</v>
+        <v>0.57130896027580525</v>
       </c>
       <c r="J3" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>120.17772092426242</v>
+        <v>135.77640705286899</v>
       </c>
       <c r="L3" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M3" s="0">
         <v>15</v>
       </c>
       <c r="N3" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O3" s="0">
-        <v>42.931378255005832</v>
+        <v>47.312316197331356</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -315,43 +315,43 @@
         <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>0.225783489151373</v>
+        <v>0.28196266666666664</v>
       </c>
       <c r="D4" s="0">
-        <v>4.2840632783572508</v>
+        <v>3.8135626666666673</v>
       </c>
       <c r="E4" s="0">
-        <v>13.724994100341393</v>
+        <v>10.179992831559309</v>
       </c>
       <c r="F4" s="0">
-        <v>10.073182996903961</v>
+        <v>9.2683539830774482</v>
       </c>
       <c r="G4" s="0">
-        <v>5.3539603015768265</v>
+        <v>6.1089954865629936</v>
       </c>
       <c r="H4" s="0">
-        <v>5.6033288089873441</v>
+        <v>4.9107909910862322</v>
       </c>
       <c r="I4" s="0">
-        <v>0.72461296185796842</v>
+        <v>0.61344817041332378</v>
       </c>
       <c r="J4" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>127.13542137442248</v>
+        <v>145.32159304591025</v>
       </c>
       <c r="L4" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M4" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N4" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O4" s="0">
-        <v>42.952385342180236</v>
+        <v>47.310803963747446</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -365,43 +365,43 @@
         <v>6</v>
       </c>
       <c r="C5" s="0">
-        <v>0.43156697830274604</v>
+        <v>0.54392533333333326</v>
       </c>
       <c r="D5" s="0">
-        <v>4.4898467675086238</v>
+        <v>4.0755253333333341</v>
       </c>
       <c r="E5" s="0">
-        <v>15.198030002843097</v>
+        <v>11.852859623925781</v>
       </c>
       <c r="F5" s="0">
-        <v>10.312276400324862</v>
+        <v>9.5813999086613855</v>
       </c>
       <c r="G5" s="0">
-        <v>5.0482712875213078</v>
+        <v>5.638067041475253</v>
       </c>
       <c r="H5" s="0">
-        <v>5.9426283357941223</v>
+        <v>5.3209725566069572</v>
       </c>
       <c r="I5" s="0">
-        <v>0.75941949338815185</v>
+        <v>0.65558738055084242</v>
       </c>
       <c r="J5" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>134.41831511139935</v>
+        <v>155.55185833447797</v>
       </c>
       <c r="L5" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M5" s="0">
         <v>14</v>
       </c>
       <c r="N5" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O5" s="0">
-        <v>42.969426477571155</v>
+        <v>47.336755758061841</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -415,43 +415,43 @@
         <v>7</v>
       </c>
       <c r="C6" s="0">
-        <v>0.63735046745411894</v>
+        <v>0.80588799999999983</v>
       </c>
       <c r="D6" s="0">
-        <v>4.6956302566599968</v>
+        <v>4.3374880000000005</v>
       </c>
       <c r="E6" s="0">
-        <v>16.797229211998935</v>
+        <v>13.546729712421424</v>
       </c>
       <c r="F6" s="0">
-        <v>10.545950569971355</v>
+        <v>9.8845365528063667</v>
       </c>
       <c r="G6" s="0">
-        <v>4.7670589433933594</v>
+        <v>5.2198765430309857</v>
       </c>
       <c r="H6" s="0">
-        <v>6.2931883906274821</v>
+        <v>5.7472623639064322</v>
       </c>
       <c r="I6" s="0">
-        <v>0.79422602491833561</v>
+        <v>0.69772659068836074</v>
       </c>
       <c r="J6" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>142.026402135193</v>
+        <v>166.42031906845483</v>
       </c>
       <c r="L6" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M6" s="0">
         <v>13</v>
       </c>
       <c r="N6" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O6" s="0">
-        <v>42.984319308042402</v>
+        <v>47.362437030097695</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -465,43 +465,43 @@
         <v>8</v>
       </c>
       <c r="C7" s="0">
-        <v>0.84313395660549206</v>
+        <v>1.0678506666666665</v>
       </c>
       <c r="D7" s="0">
-        <v>4.9014137458113698</v>
+        <v>4.5994506666666668</v>
       </c>
       <c r="E7" s="0">
-        <v>18.407660459232378</v>
+        <v>15.366654899182031</v>
       </c>
       <c r="F7" s="0">
-        <v>10.774558101929806</v>
+        <v>10.178649297320051</v>
       </c>
       <c r="G7" s="0">
-        <v>4.5072615194675327</v>
+        <v>4.8454856226895497</v>
       </c>
       <c r="H7" s="0">
-        <v>6.6559261916410968</v>
+        <v>6.1913298967437882</v>
       </c>
       <c r="I7" s="0">
-        <v>0.82903255644851914</v>
+        <v>0.73986580082587927</v>
       </c>
       <c r="J7" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>150.40643290956771</v>
+        <v>177.92697524784114</v>
       </c>
       <c r="L7" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M7" s="0">
         <v>12</v>
       </c>
       <c r="N7" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O7" s="0">
-        <v>42.995202336864317</v>
+        <v>47.387052688393126</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -515,43 +515,43 @@
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <v>1.0489174457568651</v>
+        <v>1.3298133333333331</v>
       </c>
       <c r="D8" s="0">
-        <v>5.1071972349627437</v>
+        <v>4.8614133333333331</v>
       </c>
       <c r="E8" s="0">
-        <v>20.147138361395392</v>
+        <v>17.430553919578038</v>
       </c>
       <c r="F8" s="0">
-        <v>10.998414938501062</v>
+        <v>10.464499040656593</v>
       </c>
       <c r="G8" s="0">
-        <v>4.2663089622887034</v>
+        <v>4.5077863189613696</v>
       </c>
       <c r="H8" s="0">
-        <v>7.0318395280744515</v>
+        <v>6.6551513042686201</v>
       </c>
       <c r="I8" s="0">
-        <v>0.8638390879787029</v>
+        <v>0.7820050109633977</v>
       </c>
       <c r="J8" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>159.20367818881724</v>
+        <v>190.1585580228757</v>
       </c>
       <c r="L8" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M8" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N8" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O8" s="0">
-        <v>43.005879839622558</v>
+        <v>47.413327913350564</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -565,43 +565,43 @@
         <v>10</v>
       </c>
       <c r="C9" s="0">
-        <v>1.2547009349082379</v>
+        <v>1.5917759999999996</v>
       </c>
       <c r="D9" s="0">
-        <v>5.3129807241141158</v>
+        <v>5.1233760000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>22.019371525012144</v>
+        <v>19.51275320490431</v>
       </c>
       <c r="F9" s="0">
-        <v>11.217805490693149</v>
+        <v>10.742745404503058</v>
       </c>
       <c r="G9" s="0">
-        <v>4.0420279751870716</v>
+        <v>4.2012061396489928</v>
       </c>
       <c r="H9" s="0">
-        <v>7.4220169143217154</v>
+        <v>7.140806473853833</v>
       </c>
       <c r="I9" s="0">
-        <v>0.89864561950888644</v>
+        <v>0.82414422110091623</v>
       </c>
       <c r="J9" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>168.34733192642676</v>
+        <v>203.41224415814975</v>
       </c>
       <c r="L9" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M9" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N9" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O9" s="0">
-        <v>43.016059103366388</v>
+        <v>47.435208206028747</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -615,43 +615,43 @@
         <v>11</v>
       </c>
       <c r="C10" s="0">
-        <v>1.4604844240596111</v>
+        <v>1.8537386666666662</v>
       </c>
       <c r="D10" s="0">
-        <v>5.5187642132654897</v>
+        <v>5.3853386666666667</v>
       </c>
       <c r="E10" s="0">
-        <v>24.027993990189661</v>
+        <v>21.849308561644751</v>
       </c>
       <c r="F10" s="0">
-        <v>11.432986875467297</v>
+        <v>11.013964657653499</v>
       </c>
       <c r="G10" s="0">
-        <v>3.8324748357738301</v>
+        <v>3.9213180361332398</v>
       </c>
       <c r="H10" s="0">
-        <v>7.8278400473678733</v>
+        <v>7.6504888722524038</v>
       </c>
       <c r="I10" s="0">
-        <v>0.9334521510390702</v>
+        <v>0.86628343123843465</v>
       </c>
       <c r="J10" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>177.83739412239646</v>
+        <v>217.32762246118017</v>
       </c>
       <c r="L10" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M10" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N10" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O10" s="0">
-        <v>43.024965917964153</v>
+        <v>47.454678123096983</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -665,46 +665,46 @@
         <v>12</v>
       </c>
       <c r="C11" s="0">
-        <v>1.6662679132109841</v>
+        <v>2.115701333333333</v>
       </c>
       <c r="D11" s="0">
-        <v>5.7245477024168618</v>
+        <v>5.6473013333333331</v>
       </c>
       <c r="E11" s="0">
-        <v>26.176540729946396</v>
+        <v>24.326533360710485</v>
       </c>
       <c r="F11" s="0">
-        <v>11.64419244783379</v>
+        <v>11.278663756585226</v>
       </c>
       <c r="G11" s="0">
-        <v>3.6361713760615975</v>
+        <v>3.66445051893874</v>
       </c>
       <c r="H11" s="0">
-        <v>8.2504362136235549</v>
+        <v>8.1867662955067786</v>
       </c>
       <c r="I11" s="0">
-        <v>0.96825868256925363</v>
+        <v>0.90842264137595319</v>
       </c>
       <c r="J11" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>187.67386477672636</v>
+        <v>231.90469293196711</v>
       </c>
       <c r="L11" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M11" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N11" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O11" s="0">
-        <v>43.031336250966703</v>
+        <v>47.468581589712699</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -715,43 +715,43 @@
         <v>13</v>
       </c>
       <c r="C12" s="0">
-        <v>1.8720514023623571</v>
+        <v>2.3776639999999993</v>
       </c>
       <c r="D12" s="0">
-        <v>5.9303311915682357</v>
+        <v>5.9092640000000003</v>
       </c>
       <c r="E12" s="0">
-        <v>28.337621085749401</v>
+        <v>26.946078069556002</v>
       </c>
       <c r="F12" s="0">
-        <v>11.851634766131278</v>
+        <v>11.537291484060631</v>
       </c>
       <c r="G12" s="0">
-        <v>3.4516349146667103</v>
+        <v>3.4275127466428996</v>
       </c>
       <c r="H12" s="0">
-        <v>8.6915333578658043</v>
+        <v>8.7527026790443596</v>
       </c>
       <c r="I12" s="0">
-        <v>1.0030652140994376</v>
+        <v>0.95056185151347161</v>
       </c>
       <c r="J12" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>198.60832196045709</v>
+        <v>247.38541601008501</v>
       </c>
       <c r="L12" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M12" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N12" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O12" s="0">
-        <v>43.035632453032314</v>
+        <v>47.481627747069965</v>
       </c>
       <c r="P12" s="0" t="s">
         <v>35</v>
@@ -765,43 +765,43 @@
         <v>14</v>
       </c>
       <c r="C13" s="0">
-        <v>2.0778348915137301</v>
+        <v>2.6396266666666661</v>
       </c>
       <c r="D13" s="0">
-        <v>6.1361146807196079</v>
+        <v>6.1712266666666666</v>
       </c>
       <c r="E13" s="0">
-        <v>30.640644851482932</v>
+        <v>29.709480129804522</v>
       </c>
       <c r="F13" s="0">
-        <v>12.055508097851106</v>
+        <v>11.79024738681283</v>
       </c>
       <c r="G13" s="0">
-        <v>3.2778014729258609</v>
+        <v>3.2079985131635045</v>
       </c>
       <c r="H13" s="0">
-        <v>9.152476209372475</v>
+        <v>9.3516252819007981</v>
       </c>
       <c r="I13" s="0">
-        <v>1.0378717456296209</v>
+        <v>0.99270106165099015</v>
       </c>
       <c r="J13" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>209.91799351720425</v>
+        <v>263.73864142446382</v>
       </c>
       <c r="L13" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M13" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O13" s="0">
-        <v>43.035632453032307</v>
+        <v>47.494073084957236</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -815,43 +815,43 @@
         <v>15</v>
       </c>
       <c r="C14" s="0">
-        <v>2.2836183806651031</v>
+        <v>2.9015893333333325</v>
       </c>
       <c r="D14" s="0">
-        <v>6.3418981698709818</v>
+        <v>6.433189333333333</v>
       </c>
       <c r="E14" s="0">
-        <v>32.953706077207592</v>
+        <v>32.618163474446</v>
       </c>
       <c r="F14" s="0">
-        <v>12.255990550132442</v>
+        <v>12.037889021598245</v>
       </c>
       <c r="G14" s="0">
-        <v>3.1136853363123116</v>
+        <v>3.0038076362539674</v>
       </c>
       <c r="H14" s="0">
-        <v>9.634884954537652</v>
+        <v>9.9873239677267893</v>
       </c>
       <c r="I14" s="0">
-        <v>1.0726782771598047</v>
+        <v>1.0348402717885083</v>
       </c>
       <c r="J14" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>221.59974778724984</v>
+        <v>280.77240090570217</v>
       </c>
       <c r="L14" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M14" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O14" s="0">
-        <v>43.035632453032299</v>
+        <v>47.504967208696982</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -865,43 +865,43 @@
         <v>16</v>
       </c>
       <c r="C15" s="0">
-        <v>2.4894018698164757</v>
+        <v>3.1635519999999993</v>
       </c>
       <c r="D15" s="0">
-        <v>6.5476816590223539</v>
+        <v>6.6951520000000002</v>
       </c>
       <c r="E15" s="0">
-        <v>35.547721618663054</v>
+        <v>35.808605395088385</v>
       </c>
       <c r="F15" s="0">
-        <v>12.453245891433998</v>
+        <v>12.280537885222468</v>
       </c>
       <c r="G15" s="0">
-        <v>2.9583332474096187</v>
+        <v>2.8131668556260054</v>
       </c>
       <c r="H15" s="0">
-        <v>10.140845364959697</v>
+        <v>10.664138154480066</v>
       </c>
       <c r="I15" s="0">
-        <v>1.107484808689988</v>
+        <v>1.0769794819260272</v>
       </c>
       <c r="J15" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K15" s="0">
-        <v>233.65358477059323</v>
+        <v>298.58519042477383</v>
       </c>
       <c r="L15" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M15" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N15" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O15" s="0">
-        <v>43.036936113503174</v>
+        <v>47.515864855608122</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -915,43 +915,43 @@
         <v>17</v>
       </c>
       <c r="C16" s="0">
-        <v>2.6951853589678492</v>
+        <v>3.4255146666666661</v>
       </c>
       <c r="D16" s="0">
-        <v>6.7534651481737278</v>
+        <v>6.9571146666666666</v>
       </c>
       <c r="E16" s="0">
-        <v>38.153453445181071</v>
+        <v>39.151863996229935</v>
       </c>
       <c r="F16" s="0">
-        <v>12.647425117394443</v>
+        <v>12.518484309390381</v>
       </c>
       <c r="G16" s="0">
-        <v>2.8109526881963296</v>
+        <v>2.6345564286847911</v>
       </c>
       <c r="H16" s="0">
-        <v>10.672538220218051</v>
+        <v>11.387116128302644</v>
       </c>
       <c r="I16" s="0">
-        <v>1.1422913402201718</v>
+        <v>1.1191186920635456</v>
       </c>
       <c r="J16" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K16" s="0">
-        <v>246.47290940500514</v>
+        <v>318.56554326050531</v>
       </c>
       <c r="L16" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M16" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O16" s="0">
-        <v>43.038213963404566</v>
+        <v>47.519840358423792</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -965,43 +965,43 @@
         <v>18</v>
       </c>
       <c r="C17" s="0">
-        <v>2.9009688481192222</v>
+        <v>3.6874773333333324</v>
       </c>
       <c r="D17" s="0">
-        <v>6.9592486373250999</v>
+        <v>7.2190773333333329</v>
       </c>
       <c r="E17" s="0">
-        <v>40.908783653975469</v>
+        <v>42.648736940877868</v>
       </c>
       <c r="F17" s="0">
-        <v>12.838667803463172</v>
+        <v>12.751991533032083</v>
       </c>
       <c r="G17" s="0">
-        <v>2.6711156204248723</v>
+        <v>2.4666976089264336</v>
       </c>
       <c r="H17" s="0">
-        <v>11.231262237621952</v>
+        <v>12.162009599975542</v>
       </c>
       <c r="I17" s="0">
-        <v>1.1770978717503555</v>
+        <v>1.1612579022010638</v>
       </c>
       <c r="J17" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K17" s="0">
-        <v>259.94824678259948</v>
+        <v>339.28508817007446</v>
       </c>
       <c r="L17" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M17" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N17" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O17" s="0">
-        <v>43.038530844657828</v>
+        <v>47.523615217891397</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1015,43 +1015,43 @@
         <v>19</v>
       </c>
       <c r="C18" s="0">
-        <v>3.1067523372705952</v>
+        <v>3.9494399999999992</v>
       </c>
       <c r="D18" s="0">
-        <v>7.1650321264764738</v>
+        <v>7.4810400000000001</v>
       </c>
       <c r="E18" s="0">
-        <v>43.816424986732407</v>
+        <v>46.442810839449578</v>
       </c>
       <c r="F18" s="0">
-        <v>13.027103278751726</v>
+        <v>12.981299114980393</v>
       </c>
       <c r="G18" s="0">
-        <v>2.5380449372512981</v>
+        <v>2.3085469513483807</v>
       </c>
       <c r="H18" s="0">
-        <v>11.820121684878437</v>
+        <v>12.995187289770104</v>
       </c>
       <c r="I18" s="0">
-        <v>1.2119044032805393</v>
+        <v>1.2033971123385825</v>
       </c>
       <c r="J18" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K18" s="0">
-        <v>273.81535937115746</v>
+        <v>360.74382515348179</v>
       </c>
       <c r="L18" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M18" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N18" s="0">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O18" s="0">
-        <v>43.038208225227038</v>
+        <v>47.527216162971612</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-05 21:45)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 09:50)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-05 21:45</t>
+    <t>2026-10-06 09:50</t>
   </si>
   <si>
     <t>Iteration</t>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 09:50)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 10:59)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-06 09:50</t>
+    <t>2026-10-06 10:59</t>
   </si>
   <si>
     <t>Iteration</t>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -6,8 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Deliverable 8" sheetId="1" r:id="rId2"/>
+    <sheet name="Deliverable 8" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
@@ -15,13 +16,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 09:50)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 13:55)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-06 09:50</t>
+    <t>2026-10-06 13:55</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -164,27 +165,27 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" customWidth="true"/>
-    <col min="2" max="2" width="9.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
-    <col min="4" max="4" width="11.5546875" customWidth="true"/>
-    <col min="5" max="5" width="11.5546875" customWidth="true"/>
-    <col min="6" max="6" width="11.5546875" customWidth="true"/>
-    <col min="7" max="7" width="13.33203125" customWidth="true"/>
-    <col min="8" max="8" width="11.5546875" customWidth="true"/>
-    <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="11.5546875" customWidth="true"/>
-    <col min="11" max="11" width="12.77734375" customWidth="true"/>
-    <col min="12" max="12" width="13.88671875" customWidth="true"/>
-    <col min="13" max="13" width="11.21875" customWidth="true"/>
-    <col min="14" max="14" width="12.88671875" customWidth="true"/>
-    <col min="15" max="15" width="13.109375" customWidth="true"/>
-    <col min="16" max="16" width="11.77734375" customWidth="true"/>
+    <col min="1" max="1" width="61.7109375" customWidth="true"/>
+    <col min="2" max="2" width="10.140625" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="14.28515625" customWidth="true"/>
+    <col min="8" max="8" width="11.7109375" customWidth="true"/>
+    <col min="9" max="9" width="12.7109375" customWidth="true"/>
+    <col min="10" max="10" width="11.7109375" customWidth="true"/>
+    <col min="11" max="11" width="13.85546875" customWidth="true"/>
+    <col min="12" max="12" width="15" customWidth="true"/>
+    <col min="13" max="13" width="12.42578125" customWidth="true"/>
+    <col min="14" max="14" width="14" customWidth="true"/>
+    <col min="15" max="15" width="14.42578125" customWidth="true"/>
+    <col min="16" max="16" width="13.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -271,25 +272,25 @@
         <v>3.5516000000000005</v>
       </c>
       <c r="E3" s="0">
-        <v>8.7337587366424181</v>
+        <v>8.8232251675073083</v>
       </c>
       <c r="F3" s="0">
-        <v>8.9443583840071384</v>
+        <v>8.9443583840071383</v>
       </c>
       <c r="G3" s="0">
-        <v>6.6442450244202726</v>
+        <v>6.6307892150904122</v>
       </c>
       <c r="H3" s="0">
-        <v>4.5151856817046836</v>
+        <v>4.5243483131277529</v>
       </c>
       <c r="I3" s="0">
-        <v>0.57130896027580525</v>
+        <v>0.57130896027580524</v>
       </c>
       <c r="J3" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>135.77640705286899</v>
+        <v>138.54430849415479</v>
       </c>
       <c r="L3" s="0">
         <v>700</v>
@@ -301,7 +302,7 @@
         <v>700</v>
       </c>
       <c r="O3" s="0">
-        <v>47.312316197331356</v>
+        <v>49.149009080062868</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -321,16 +322,16 @@
         <v>3.8135626666666673</v>
       </c>
       <c r="E4" s="0">
-        <v>10.179992831559309</v>
+        <v>10.27131493469029</v>
       </c>
       <c r="F4" s="0">
         <v>9.2683539830774482</v>
       </c>
       <c r="G4" s="0">
-        <v>6.1089954865629936</v>
+        <v>6.0964376588461153</v>
       </c>
       <c r="H4" s="0">
-        <v>4.9107909910862322</v>
+        <v>4.9209065488382535</v>
       </c>
       <c r="I4" s="0">
         <v>0.61344817041332378</v>
@@ -339,7 +340,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>145.32159304591025</v>
+        <v>148.12560672156138</v>
       </c>
       <c r="L4" s="0">
         <v>700</v>
@@ -351,7 +352,7 @@
         <v>700</v>
       </c>
       <c r="O4" s="0">
-        <v>47.310803963747446</v>
+        <v>49.153202933053109</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -371,16 +372,16 @@
         <v>4.0755253333333341</v>
       </c>
       <c r="E5" s="0">
-        <v>11.852859623925781</v>
+        <v>11.839937034637035</v>
       </c>
       <c r="F5" s="0">
         <v>9.5813999086613855</v>
       </c>
       <c r="G5" s="0">
-        <v>5.638067041475253</v>
+        <v>5.6261859724350307</v>
       </c>
       <c r="H5" s="0">
-        <v>5.3209725566069572</v>
+        <v>5.3322090927996655</v>
       </c>
       <c r="I5" s="0">
         <v>0.65558738055084242</v>
@@ -389,19 +390,19 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>155.55185833447797</v>
+        <v>158.34438371943375</v>
       </c>
       <c r="L5" s="0">
         <v>700</v>
       </c>
       <c r="M5" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5" s="0">
         <v>700</v>
       </c>
       <c r="O5" s="0">
-        <v>47.336755758061841</v>
+        <v>49.186896701200382</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -421,16 +422,16 @@
         <v>4.3374880000000005</v>
       </c>
       <c r="E6" s="0">
-        <v>13.546729712421424</v>
+        <v>13.531838338459737</v>
       </c>
       <c r="F6" s="0">
         <v>9.8845365528063667</v>
       </c>
       <c r="G6" s="0">
-        <v>5.2198765430309857</v>
+        <v>5.2086291865374754</v>
       </c>
       <c r="H6" s="0">
-        <v>5.7472623639064322</v>
+        <v>5.7596728286090588</v>
       </c>
       <c r="I6" s="0">
         <v>0.69772659068836074</v>
@@ -439,7 +440,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>166.42031906845483</v>
+        <v>169.2928808686853</v>
       </c>
       <c r="L6" s="0">
         <v>700</v>
@@ -451,7 +452,7 @@
         <v>700</v>
       </c>
       <c r="O6" s="0">
-        <v>47.362437030097695</v>
+        <v>49.216150312022101</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -471,16 +472,16 @@
         <v>4.5994506666666668</v>
       </c>
       <c r="E7" s="0">
-        <v>15.366654899182031</v>
+        <v>15.349630568700421</v>
       </c>
       <c r="F7" s="0">
         <v>10.178649297320051</v>
       </c>
       <c r="G7" s="0">
-        <v>4.8454856226895497</v>
+        <v>4.8347065472532718</v>
       </c>
       <c r="H7" s="0">
-        <v>6.1913298967437882</v>
+        <v>6.2051335912091323</v>
       </c>
       <c r="I7" s="0">
         <v>0.73986580082587927</v>
@@ -489,7 +490,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>177.92697524784114</v>
+        <v>180.94280389518167</v>
       </c>
       <c r="L7" s="0">
         <v>700</v>
@@ -501,7 +502,7 @@
         <v>700</v>
       </c>
       <c r="O7" s="0">
-        <v>47.387052688393126</v>
+        <v>49.243868599508474</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -521,16 +522,16 @@
         <v>4.8614133333333331</v>
       </c>
       <c r="E8" s="0">
-        <v>17.430553919578038</v>
+        <v>17.411096249778872</v>
       </c>
       <c r="F8" s="0">
         <v>10.464499040656593</v>
       </c>
       <c r="G8" s="0">
-        <v>4.5077863189613696</v>
+        <v>4.4974574081686791</v>
       </c>
       <c r="H8" s="0">
-        <v>6.6551513042686201</v>
+        <v>6.670435598903361</v>
       </c>
       <c r="I8" s="0">
         <v>0.7820050109633977</v>
@@ -539,7 +540,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>190.1585580228757</v>
+        <v>193.23886839831297</v>
       </c>
       <c r="L8" s="0">
         <v>700</v>
@@ -551,7 +552,7 @@
         <v>700</v>
       </c>
       <c r="O8" s="0">
-        <v>47.413327913350564</v>
+        <v>49.273094525574372</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -571,16 +572,16 @@
         <v>5.1233760000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>19.51275320490431</v>
+        <v>19.609303074267707</v>
       </c>
       <c r="F9" s="0">
         <v>10.742745404503058</v>
       </c>
       <c r="G9" s="0">
-        <v>4.2012061396489928</v>
+        <v>4.1913270456081415</v>
       </c>
       <c r="H9" s="0">
-        <v>7.140806473853833</v>
+        <v>7.1576375867484101</v>
       </c>
       <c r="I9" s="0">
         <v>0.82414422110091623</v>
@@ -589,7 +590,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>203.41224415814975</v>
+        <v>206.18107437807913</v>
       </c>
       <c r="L9" s="0">
         <v>700</v>
@@ -601,7 +602,7 @@
         <v>700</v>
       </c>
       <c r="O9" s="0">
-        <v>47.435208206028747</v>
+        <v>49.298227618402052</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -621,16 +622,16 @@
         <v>5.3853386666666667</v>
       </c>
       <c r="E10" s="0">
-        <v>21.849308561644751</v>
+        <v>21.824595167673817</v>
       </c>
       <c r="F10" s="0">
         <v>11.013964657653499</v>
       </c>
       <c r="G10" s="0">
-        <v>3.9213180361332398</v>
+        <v>3.9117588411844002</v>
       </c>
       <c r="H10" s="0">
-        <v>7.6504888722524038</v>
+        <v>7.6691844303256218</v>
       </c>
       <c r="I10" s="0">
         <v>0.86628343123843465</v>
@@ -639,7 +640,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>217.32762246118017</v>
+        <v>220.03442265863271</v>
       </c>
       <c r="L10" s="0">
         <v>700</v>
@@ -651,7 +652,7 @@
         <v>700</v>
       </c>
       <c r="O10" s="0">
-        <v>47.454678123096983</v>
+        <v>49.317334412625186</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -671,16 +672,16 @@
         <v>5.6473013333333331</v>
       </c>
       <c r="E11" s="0">
-        <v>24.326533360710485</v>
+        <v>24.298852727894275</v>
       </c>
       <c r="F11" s="0">
         <v>11.278663756585226</v>
       </c>
       <c r="G11" s="0">
-        <v>3.66445051893874</v>
+        <v>3.6552722921511758</v>
       </c>
       <c r="H11" s="0">
-        <v>8.1867662955067786</v>
+        <v>8.2073229029798505</v>
       </c>
       <c r="I11" s="0">
         <v>0.90842264137595319</v>
@@ -689,7 +690,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>231.90469293196711</v>
+        <v>234.75095847596126</v>
       </c>
       <c r="L11" s="0">
         <v>700</v>
@@ -701,7 +702,7 @@
         <v>700</v>
       </c>
       <c r="O11" s="0">
-        <v>47.468581589712699</v>
+        <v>49.33431750090763</v>
       </c>
       <c r="P11" s="0" t="s">
         <v>34</v>
@@ -721,16 +722,16 @@
         <v>5.9092640000000003</v>
       </c>
       <c r="E12" s="0">
-        <v>26.946078069556002</v>
+        <v>26.915249119227788</v>
       </c>
       <c r="F12" s="0">
         <v>11.537291484060631</v>
       </c>
       <c r="G12" s="0">
-        <v>3.4275127466428996</v>
+        <v>3.4187017707153449</v>
       </c>
       <c r="H12" s="0">
-        <v>8.7527026790443596</v>
+        <v>8.775260906634351</v>
       </c>
       <c r="I12" s="0">
         <v>0.95056185151347161</v>
@@ -739,7 +740,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>247.38541601008501</v>
+        <v>250.13551716567326</v>
       </c>
       <c r="L12" s="0">
         <v>700</v>
@@ -751,7 +752,7 @@
         <v>700</v>
       </c>
       <c r="O12" s="0">
-        <v>47.481627747069965</v>
+        <v>49.349622124678028</v>
       </c>
       <c r="P12" s="0" t="s">
         <v>35</v>
@@ -771,16 +772,16 @@
         <v>6.1712266666666666</v>
       </c>
       <c r="E13" s="0">
-        <v>29.709480129804522</v>
+        <v>29.805240278006369</v>
       </c>
       <c r="F13" s="0">
         <v>11.79024738681283</v>
       </c>
       <c r="G13" s="0">
-        <v>3.2079985131635045</v>
+        <v>3.1995246096546985</v>
       </c>
       <c r="H13" s="0">
-        <v>9.3516252819007981</v>
+        <v>9.3763929520884925</v>
       </c>
       <c r="I13" s="0">
         <v>0.99270106165099015</v>
@@ -789,7 +790,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>263.73864142446382</v>
+        <v>266.18809872776905</v>
       </c>
       <c r="L13" s="0">
         <v>700</v>
@@ -801,7 +802,7 @@
         <v>700</v>
       </c>
       <c r="O13" s="0">
-        <v>47.494073084957236</v>
+        <v>49.365219864654513</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -821,16 +822,16 @@
         <v>6.433189333333333</v>
       </c>
       <c r="E14" s="0">
-        <v>32.618163474446</v>
+        <v>32.712999919445906</v>
       </c>
       <c r="F14" s="0">
         <v>12.037889021598245</v>
       </c>
       <c r="G14" s="0">
-        <v>3.0038076362539674</v>
+        <v>2.9956442308659361</v>
       </c>
       <c r="H14" s="0">
-        <v>9.9873239677267893</v>
+        <v>10.014540341904368</v>
       </c>
       <c r="I14" s="0">
         <v>1.0348402717885083</v>
@@ -839,7 +840,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>280.77240090570217</v>
+        <v>283.8034731590929</v>
       </c>
       <c r="L14" s="0">
         <v>700</v>
@@ -851,7 +852,7 @@
         <v>700</v>
       </c>
       <c r="O14" s="0">
-        <v>47.504967208696982</v>
+        <v>49.374522353360589</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -871,16 +872,16 @@
         <v>6.6951520000000002</v>
       </c>
       <c r="E15" s="0">
-        <v>35.808605395088385</v>
+        <v>35.902301983572507</v>
       </c>
       <c r="F15" s="0">
         <v>12.280537885222468</v>
       </c>
       <c r="G15" s="0">
-        <v>2.8131668556260054</v>
+        <v>2.8052904225407285</v>
       </c>
       <c r="H15" s="0">
-        <v>10.664138154480066</v>
+        <v>10.694079928034419</v>
       </c>
       <c r="I15" s="0">
         <v>1.0769794819260272</v>
@@ -889,19 +890,19 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K15" s="0">
-        <v>298.58519042477383</v>
+        <v>302.28017769690871</v>
       </c>
       <c r="L15" s="0">
         <v>700</v>
       </c>
       <c r="M15" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N15" s="0">
         <v>700</v>
       </c>
       <c r="O15" s="0">
-        <v>47.515864855608122</v>
+        <v>49.383835957714609</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -915,22 +916,22 @@
         <v>17</v>
       </c>
       <c r="C16" s="0">
-        <v>3.4255146666666661</v>
+        <v>3.425514666666666</v>
       </c>
       <c r="D16" s="0">
         <v>6.9571146666666666</v>
       </c>
       <c r="E16" s="0">
-        <v>39.151863996229935</v>
+        <v>39.244112344375601</v>
       </c>
       <c r="F16" s="0">
         <v>12.518484309390381</v>
       </c>
       <c r="G16" s="0">
-        <v>2.6345564286847911</v>
+        <v>2.6270430910328191</v>
       </c>
       <c r="H16" s="0">
-        <v>11.387116128302644</v>
+        <v>11.419683256206328</v>
       </c>
       <c r="I16" s="0">
         <v>1.1191186920635456</v>
@@ -939,7 +940,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K16" s="0">
-        <v>318.56554326050531</v>
+        <v>321.46670601895494</v>
       </c>
       <c r="L16" s="0">
         <v>700</v>
@@ -951,7 +952,7 @@
         <v>700</v>
       </c>
       <c r="O16" s="0">
-        <v>47.519840358423792</v>
+        <v>49.389729638668662</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -971,16 +972,16 @@
         <v>7.2190773333333329</v>
       </c>
       <c r="E17" s="0">
-        <v>42.648736940877868</v>
+        <v>42.739238509399961</v>
       </c>
       <c r="F17" s="0">
         <v>12.751991533032083</v>
       </c>
       <c r="G17" s="0">
-        <v>2.4666976089264336</v>
+        <v>2.459584526247053</v>
       </c>
       <c r="H17" s="0">
-        <v>12.162009599975542</v>
+        <v>12.197181954862668</v>
       </c>
       <c r="I17" s="0">
         <v>1.1612579022010638</v>
@@ -989,7 +990,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K17" s="0">
-        <v>339.28508817007446</v>
+        <v>341.78021264219217</v>
       </c>
       <c r="L17" s="0">
         <v>700</v>
@@ -1001,7 +1002,7 @@
         <v>700</v>
       </c>
       <c r="O17" s="0">
-        <v>47.523615217891397</v>
+        <v>49.395209698432986</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1021,16 +1022,16 @@
         <v>7.4810400000000001</v>
       </c>
       <c r="E18" s="0">
-        <v>46.442810839449578</v>
+        <v>46.531296178476246</v>
       </c>
       <c r="F18" s="0">
         <v>12.981299114980393</v>
       </c>
       <c r="G18" s="0">
-        <v>2.3085469513483807</v>
+        <v>2.3017499206269507</v>
       </c>
       <c r="H18" s="0">
-        <v>12.995187289770104</v>
+        <v>13.033561870104725</v>
       </c>
       <c r="I18" s="0">
         <v>1.2033971123385825</v>
@@ -1039,7 +1040,7 @@
         <v>1.1818181818181817</v>
       </c>
       <c r="K18" s="0">
-        <v>360.74382515348179</v>
+        <v>363.42343608462318</v>
       </c>
       <c r="L18" s="0">
         <v>700</v>
@@ -1051,7 +1052,7 @@
         <v>700</v>
       </c>
       <c r="O18" s="0">
-        <v>47.527216162971612</v>
+        <v>49.39968393196898</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 10:59)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:12)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-06 10:59</t>
+    <t>2026-10-06 17:12</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -178,7 +178,7 @@
     <col min="7" max="7" width="13.33203125" customWidth="true"/>
     <col min="8" max="8" width="11.5546875" customWidth="true"/>
     <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="11.5546875" customWidth="true"/>
+    <col min="10" max="10" width="12.5546875" customWidth="true"/>
     <col min="11" max="11" width="12.77734375" customWidth="true"/>
     <col min="12" max="12" width="13.88671875" customWidth="true"/>
     <col min="13" max="13" width="11.21875" customWidth="true"/>
@@ -271,37 +271,37 @@
         <v>3.5516000000000005</v>
       </c>
       <c r="E3" s="0">
-        <v>8.7337587366424181</v>
+        <v>9.7054627078670261</v>
       </c>
       <c r="F3" s="0">
-        <v>8.9443583840071384</v>
+        <v>9.1755117785210558</v>
       </c>
       <c r="G3" s="0">
-        <v>6.6442450244202726</v>
+        <v>8.7562819237403886</v>
       </c>
       <c r="H3" s="0">
-        <v>4.5151856817046836</v>
+        <v>3.426111706004209</v>
       </c>
       <c r="I3" s="0">
-        <v>0.57130896027580525</v>
+        <v>0.60121975882544754</v>
       </c>
       <c r="J3" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K3" s="0">
-        <v>135.77640705286899</v>
+        <v>135.02738031237274</v>
       </c>
       <c r="L3" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M3" s="0">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N3" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O3" s="0">
-        <v>47.312316197331356</v>
+        <v>57.387402365607144</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -321,37 +321,37 @@
         <v>3.8135626666666673</v>
       </c>
       <c r="E4" s="0">
-        <v>10.179992831559309</v>
+        <v>11.345630480908152</v>
       </c>
       <c r="F4" s="0">
-        <v>9.2683539830774482</v>
+        <v>9.5078805530967863</v>
       </c>
       <c r="G4" s="0">
-        <v>6.1089954865629936</v>
+        <v>8.0822729253608383</v>
       </c>
       <c r="H4" s="0">
-        <v>4.9107909910862322</v>
+        <v>3.7118271403412959</v>
       </c>
       <c r="I4" s="0">
-        <v>0.61344817041332378</v>
+        <v>0.64556516125663477</v>
       </c>
       <c r="J4" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K4" s="0">
-        <v>145.32159304591025</v>
+        <v>144.5143111265308</v>
       </c>
       <c r="L4" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M4" s="0">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N4" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O4" s="0">
-        <v>47.310803963747446</v>
+        <v>57.428365419775084</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -371,37 +371,37 @@
         <v>4.0755253333333341</v>
       </c>
       <c r="E5" s="0">
-        <v>11.852859623925781</v>
+        <v>13.005651207035349</v>
       </c>
       <c r="F5" s="0">
-        <v>9.5813999086613855</v>
+        <v>9.8290166764602382</v>
       </c>
       <c r="G5" s="0">
-        <v>5.638067041475253</v>
+        <v>7.4908448594616202</v>
       </c>
       <c r="H5" s="0">
-        <v>5.3209725566069572</v>
+        <v>4.0048887091964351</v>
       </c>
       <c r="I5" s="0">
-        <v>0.65558738055084242</v>
+        <v>0.68991056368782211</v>
       </c>
       <c r="J5" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K5" s="0">
-        <v>155.55185833447797</v>
+        <v>154.63786570742494</v>
       </c>
       <c r="L5" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M5" s="0">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N5" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O5" s="0">
-        <v>47.336755758061841</v>
+        <v>57.459057383418973</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -421,37 +421,37 @@
         <v>4.3374880000000005</v>
       </c>
       <c r="E6" s="0">
-        <v>13.546729712421424</v>
+        <v>14.921768396904675</v>
       </c>
       <c r="F6" s="0">
-        <v>9.8845365528063667</v>
+        <v>10.139987428015424</v>
       </c>
       <c r="G6" s="0">
-        <v>5.2198765430309857</v>
+        <v>6.9669173637449893</v>
       </c>
       <c r="H6" s="0">
-        <v>5.7472623639064322</v>
+        <v>4.3060651409641286</v>
       </c>
       <c r="I6" s="0">
-        <v>0.69772659068836074</v>
+        <v>0.73425596611900923</v>
       </c>
       <c r="J6" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K6" s="0">
-        <v>166.42031906845483</v>
+        <v>165.43861192394013</v>
       </c>
       <c r="L6" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M6" s="0">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N6" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O6" s="0">
-        <v>47.362437030097695</v>
+        <v>57.492073284837751</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -471,37 +471,37 @@
         <v>4.5994506666666668</v>
       </c>
       <c r="E7" s="0">
-        <v>15.366654899182031</v>
+        <v>17.107864691734932</v>
       </c>
       <c r="F7" s="0">
-        <v>10.178649297320051</v>
+        <v>10.441701070921741</v>
       </c>
       <c r="G7" s="0">
-        <v>4.8454856226895497</v>
+        <v>6.4991584764207539</v>
       </c>
       <c r="H7" s="0">
-        <v>6.1913298967437882</v>
+        <v>4.6159822242897111</v>
       </c>
       <c r="I7" s="0">
-        <v>0.73986580082587927</v>
+        <v>0.77860136855019635</v>
       </c>
       <c r="J7" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K7" s="0">
-        <v>177.92697524784114</v>
+        <v>176.99028531019502</v>
       </c>
       <c r="L7" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M7" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N7" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O7" s="0">
-        <v>47.387052688393126</v>
+        <v>57.526575853216087</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -521,37 +521,37 @@
         <v>4.8614133333333331</v>
       </c>
       <c r="E8" s="0">
-        <v>17.430553919578038</v>
+        <v>19.31870657314164</v>
       </c>
       <c r="F8" s="0">
-        <v>10.464499040656593</v>
+        <v>10.734938167901371</v>
       </c>
       <c r="G8" s="0">
-        <v>4.5077863189613696</v>
+        <v>6.078484851965813</v>
       </c>
       <c r="H8" s="0">
-        <v>6.6551513042686201</v>
+        <v>4.9354404478441447</v>
       </c>
       <c r="I8" s="0">
-        <v>0.7820050109633977</v>
+        <v>0.82294677098138347</v>
       </c>
       <c r="J8" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K8" s="0">
-        <v>190.1585580228757</v>
+        <v>189.18723355069983</v>
       </c>
       <c r="L8" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M8" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N8" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O8" s="0">
-        <v>47.413327913350564</v>
+        <v>57.554393331099241</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -571,37 +571,37 @@
         <v>5.1233760000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>19.51275320490431</v>
+        <v>21.811572645139336</v>
       </c>
       <c r="F9" s="0">
-        <v>10.742745404503058</v>
+        <v>11.020375387564757</v>
       </c>
       <c r="G9" s="0">
-        <v>4.2012061396489928</v>
+        <v>5.6977519745106511</v>
       </c>
       <c r="H9" s="0">
-        <v>7.140806473853833</v>
+        <v>5.2652344528521775</v>
       </c>
       <c r="I9" s="0">
-        <v>0.82414422110091623</v>
+        <v>0.86729217341257081</v>
       </c>
       <c r="J9" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K9" s="0">
-        <v>203.41224415814975</v>
+        <v>202.02945664545462</v>
       </c>
       <c r="L9" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M9" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N9" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O9" s="0">
-        <v>47.435208206028747</v>
+        <v>57.576598096211214</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -621,37 +621,37 @@
         <v>5.3853386666666667</v>
       </c>
       <c r="E10" s="0">
-        <v>21.849308561644751</v>
+        <v>24.326775068766846</v>
       </c>
       <c r="F10" s="0">
-        <v>11.013964657653499</v>
+        <v>11.298603891500067</v>
       </c>
       <c r="G10" s="0">
-        <v>3.9213180361332398</v>
+        <v>5.3510989524191608</v>
       </c>
       <c r="H10" s="0">
-        <v>7.6504888722524038</v>
+        <v>5.6063250309429238</v>
       </c>
       <c r="I10" s="0">
-        <v>0.86628343123843465</v>
+        <v>0.91163757584375782</v>
       </c>
       <c r="J10" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K10" s="0">
-        <v>217.32762246118017</v>
+        <v>215.63794683542687</v>
       </c>
       <c r="L10" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M10" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N10" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O10" s="0">
-        <v>47.454678123096983</v>
+        <v>57.593210034297492</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -671,40 +671,40 @@
         <v>5.6473013333333331</v>
       </c>
       <c r="E11" s="0">
-        <v>24.326533360710485</v>
+        <v>27.134881131722675</v>
       </c>
       <c r="F11" s="0">
-        <v>11.278663756585226</v>
+        <v>11.570143737706886</v>
       </c>
       <c r="G11" s="0">
-        <v>3.66445051893874</v>
+        <v>5.0337619473924891</v>
       </c>
       <c r="H11" s="0">
-        <v>8.1867662955067786</v>
+        <v>5.9597573968590494</v>
       </c>
       <c r="I11" s="0">
-        <v>0.90842264137595319</v>
+        <v>0.95598297827494505</v>
       </c>
       <c r="J11" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K11" s="0">
-        <v>231.90469293196711</v>
+        <v>230.24932193541821</v>
       </c>
       <c r="L11" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M11" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N11" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O11" s="0">
-        <v>47.468581589712699</v>
+        <v>57.610330207974869</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -721,37 +721,37 @@
         <v>5.9092640000000003</v>
       </c>
       <c r="E12" s="0">
-        <v>26.946078069556002</v>
+        <v>30.105011805261494</v>
       </c>
       <c r="F12" s="0">
-        <v>11.537291484060631</v>
+        <v>11.835455307058334</v>
       </c>
       <c r="G12" s="0">
-        <v>3.4275127466428996</v>
+        <v>4.7418734511692717</v>
       </c>
       <c r="H12" s="0">
-        <v>8.7527026790443596</v>
+        <v>6.3266133752688969</v>
       </c>
       <c r="I12" s="0">
-        <v>0.95056185151347161</v>
+        <v>1.0003283807061323</v>
       </c>
       <c r="J12" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K12" s="0">
-        <v>247.38541601008501</v>
+        <v>245.52782393748973</v>
       </c>
       <c r="L12" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M12" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N12" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O12" s="0">
-        <v>47.481627747069965</v>
+        <v>57.625403588221822</v>
       </c>
       <c r="P12" s="0" t="s">
         <v>35</v>
@@ -771,37 +771,37 @@
         <v>6.1712266666666666</v>
       </c>
       <c r="E13" s="0">
-        <v>29.709480129804522</v>
+        <v>33.384016233258862</v>
       </c>
       <c r="F13" s="0">
-        <v>11.79024738681283</v>
+        <v>12.094948471967653</v>
       </c>
       <c r="G13" s="0">
-        <v>3.2079985131635045</v>
+        <v>4.4722201898842044</v>
       </c>
       <c r="H13" s="0">
-        <v>9.3516252819007981</v>
+        <v>6.7080775825522947</v>
       </c>
       <c r="I13" s="0">
-        <v>0.99270106165099015</v>
+        <v>1.0446737831373194</v>
       </c>
       <c r="J13" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K13" s="0">
-        <v>263.73864142446382</v>
+        <v>261.47345284164129</v>
       </c>
       <c r="L13" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M13" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N13" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O13" s="0">
-        <v>47.494073084957236</v>
+        <v>57.639816714212508</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -821,37 +821,37 @@
         <v>6.433189333333333</v>
       </c>
       <c r="E14" s="0">
-        <v>32.618163474446</v>
+        <v>36.833993917208396</v>
       </c>
       <c r="F14" s="0">
-        <v>12.037889021598245</v>
+        <v>12.348990029704051</v>
       </c>
       <c r="G14" s="0">
-        <v>3.0038076362539674</v>
+        <v>4.2221081109388914</v>
       </c>
       <c r="H14" s="0">
-        <v>9.9873239677267893</v>
+        <v>7.1054551924604201</v>
       </c>
       <c r="I14" s="0">
-        <v>1.0348402717885083</v>
+        <v>1.0890191855685065</v>
       </c>
       <c r="J14" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K14" s="0">
-        <v>280.77240090570217</v>
+        <v>278.67921552190865</v>
       </c>
       <c r="L14" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M14" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N14" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O14" s="0">
-        <v>47.504967208696982</v>
+        <v>57.647482526514864</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -871,37 +871,37 @@
         <v>6.6951520000000002</v>
       </c>
       <c r="E15" s="0">
-        <v>35.808605395088385</v>
+        <v>40.455897887933538</v>
       </c>
       <c r="F15" s="0">
-        <v>12.280537885222468</v>
+        <v>12.597909785671094</v>
       </c>
       <c r="G15" s="0">
-        <v>2.8131668556260054</v>
+        <v>3.9892329534515283</v>
       </c>
       <c r="H15" s="0">
-        <v>10.664138154480066</v>
+        <v>7.5202427008038395</v>
       </c>
       <c r="I15" s="0">
-        <v>1.0769794819260272</v>
+        <v>1.1333645879996939</v>
       </c>
       <c r="J15" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K15" s="0">
-        <v>298.58519042477383</v>
+        <v>297.04037086874746</v>
       </c>
       <c r="L15" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M15" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N15" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O15" s="0">
-        <v>47.515864855608122</v>
+        <v>57.653839319174011</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -921,37 +921,37 @@
         <v>6.9571146666666666</v>
       </c>
       <c r="E16" s="0">
-        <v>39.151863996229935</v>
+        <v>44.404812811315189</v>
       </c>
       <c r="F16" s="0">
-        <v>12.518484309390381</v>
+        <v>12.842005574756808</v>
       </c>
       <c r="G16" s="0">
-        <v>2.6345564286847911</v>
+        <v>3.7717011233659097</v>
       </c>
       <c r="H16" s="0">
-        <v>11.387116128302644</v>
+        <v>7.9539706405017725</v>
       </c>
       <c r="I16" s="0">
-        <v>1.1191186920635456</v>
+        <v>1.177709990430881</v>
       </c>
       <c r="J16" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K16" s="0">
-        <v>318.56554326050531</v>
+        <v>316.11039796500251</v>
       </c>
       <c r="L16" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M16" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N16" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O16" s="0">
-        <v>47.519840358423792</v>
+        <v>57.659047196298609</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -971,37 +971,37 @@
         <v>7.2190773333333329</v>
       </c>
       <c r="E17" s="0">
-        <v>42.648736940877868</v>
+        <v>48.532755123995322</v>
       </c>
       <c r="F17" s="0">
-        <v>12.751991533032083</v>
+        <v>13.081547438902719</v>
       </c>
       <c r="G17" s="0">
-        <v>2.4666976089264336</v>
+        <v>3.5678602966868596</v>
       </c>
       <c r="H17" s="0">
-        <v>12.162009599975542</v>
+        <v>8.4084009757495863</v>
       </c>
       <c r="I17" s="0">
-        <v>1.1612579022010638</v>
+        <v>1.2220553928620681</v>
       </c>
       <c r="J17" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K17" s="0">
-        <v>339.28508817007446</v>
+        <v>336.03097319907522</v>
       </c>
       <c r="L17" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M17" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N17" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O17" s="0">
-        <v>47.523615217891397</v>
+        <v>57.661824530348348</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1021,37 +1021,37 @@
         <v>7.4810400000000001</v>
       </c>
       <c r="E18" s="0">
-        <v>46.442810839449578</v>
+        <v>52.999925855560832</v>
       </c>
       <c r="F18" s="0">
-        <v>12.981299114980393</v>
+        <v>13.316781127976826</v>
       </c>
       <c r="G18" s="0">
-        <v>2.3085469513483807</v>
+        <v>3.3762887364292511</v>
       </c>
       <c r="H18" s="0">
-        <v>12.995187289770104</v>
+        <v>8.8854959815219701</v>
       </c>
       <c r="I18" s="0">
-        <v>1.2033971123385825</v>
+        <v>1.2664007952932555</v>
       </c>
       <c r="J18" s="0">
-        <v>1.1818181818181817</v>
+        <v>0.99305555555555558</v>
       </c>
       <c r="K18" s="0">
-        <v>360.74382515348179</v>
+        <v>357.54983235969291</v>
       </c>
       <c r="L18" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="M18" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N18" s="0">
-        <v>700</v>
+        <v>890</v>
       </c>
       <c r="O18" s="0">
-        <v>47.527216162971612</v>
+        <v>57.663809660776543</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:12)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:16)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-06 17:12</t>
+    <t>2026-10-06 17:16</t>
   </si>
   <si>
     <t>Iteration</t>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:16)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:28)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-06 17:16</t>
+    <t>2026-10-06 17:28</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -178,7 +178,7 @@
     <col min="7" max="7" width="13.33203125" customWidth="true"/>
     <col min="8" max="8" width="11.5546875" customWidth="true"/>
     <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="11.5546875" customWidth="true"/>
     <col min="11" max="11" width="12.77734375" customWidth="true"/>
     <col min="12" max="12" width="13.88671875" customWidth="true"/>
     <col min="13" max="13" width="11.21875" customWidth="true"/>
@@ -271,37 +271,37 @@
         <v>3.5516000000000005</v>
       </c>
       <c r="E3" s="0">
-        <v>9.7054627078670261</v>
+        <v>7.5952521149320988</v>
       </c>
       <c r="F3" s="0">
-        <v>9.1755117785210558</v>
+        <v>8.9443583840071384</v>
       </c>
       <c r="G3" s="0">
-        <v>8.7562819237403886</v>
+        <v>8.6563675842085974</v>
       </c>
       <c r="H3" s="0">
-        <v>3.426111706004209</v>
+        <v>3.4656568945532746</v>
       </c>
       <c r="I3" s="0">
-        <v>0.60121975882544754</v>
+        <v>0.57130896027580525</v>
       </c>
       <c r="J3" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>135.02738031237274</v>
+        <v>138.54430849415479</v>
       </c>
       <c r="L3" s="0">
         <v>890</v>
       </c>
       <c r="M3" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3" s="0">
         <v>890</v>
       </c>
       <c r="O3" s="0">
-        <v>57.387402365607144</v>
+        <v>57.402676366410553</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -321,37 +321,37 @@
         <v>3.8135626666666673</v>
       </c>
       <c r="E4" s="0">
-        <v>11.345630480908152</v>
+        <v>8.8316229722605026</v>
       </c>
       <c r="F4" s="0">
-        <v>9.5078805530967863</v>
+        <v>9.2683539830774482</v>
       </c>
       <c r="G4" s="0">
-        <v>8.0822729253608383</v>
+        <v>7.987332385293719</v>
       </c>
       <c r="H4" s="0">
-        <v>3.7118271403412959</v>
+        <v>3.7559473617544721</v>
       </c>
       <c r="I4" s="0">
-        <v>0.64556516125663477</v>
+        <v>0.61344817041332378</v>
       </c>
       <c r="J4" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>144.5143111265308</v>
+        <v>148.12560672156138</v>
       </c>
       <c r="L4" s="0">
         <v>890</v>
       </c>
       <c r="M4" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N4" s="0">
         <v>890</v>
       </c>
       <c r="O4" s="0">
-        <v>57.428365419775084</v>
+        <v>57.391156018114955</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -371,37 +371,37 @@
         <v>4.0755253333333341</v>
       </c>
       <c r="E5" s="0">
-        <v>13.005651207035349</v>
+        <v>10.186853252299368</v>
       </c>
       <c r="F5" s="0">
-        <v>9.8290166764602382</v>
+        <v>9.5813999086613855</v>
       </c>
       <c r="G5" s="0">
-        <v>7.4908448594616202</v>
+        <v>7.4001080759168953</v>
       </c>
       <c r="H5" s="0">
-        <v>4.0048887091964351</v>
+        <v>4.0539948460526922</v>
       </c>
       <c r="I5" s="0">
-        <v>0.68991056368782211</v>
+        <v>0.65558738055084242</v>
       </c>
       <c r="J5" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>154.63786570742494</v>
+        <v>158.34438371943375</v>
       </c>
       <c r="L5" s="0">
         <v>890</v>
       </c>
       <c r="M5" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N5" s="0">
         <v>890</v>
       </c>
       <c r="O5" s="0">
-        <v>57.459057383418973</v>
+        <v>57.391791491056083</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -421,37 +421,37 @@
         <v>4.3374880000000005</v>
       </c>
       <c r="E6" s="0">
-        <v>14.921768396904675</v>
+        <v>11.664826734344313</v>
       </c>
       <c r="F6" s="0">
-        <v>10.139987428015424</v>
+        <v>9.8845365528063667</v>
       </c>
       <c r="G6" s="0">
-        <v>6.9669173637449893</v>
+        <v>6.8799370826669959</v>
       </c>
       <c r="H6" s="0">
-        <v>4.3060651409641286</v>
+        <v>4.3605049929280097</v>
       </c>
       <c r="I6" s="0">
-        <v>0.73425596611900923</v>
+        <v>0.69772659068836074</v>
       </c>
       <c r="J6" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>165.43861192394013</v>
+        <v>169.2928808686853</v>
       </c>
       <c r="L6" s="0">
         <v>890</v>
       </c>
       <c r="M6" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N6" s="0">
         <v>890</v>
       </c>
       <c r="O6" s="0">
-        <v>57.492073284837751</v>
+        <v>57.381228802001871</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -471,37 +471,37 @@
         <v>4.5994506666666668</v>
       </c>
       <c r="E7" s="0">
-        <v>17.107864691734932</v>
+        <v>13.269228622237124</v>
       </c>
       <c r="F7" s="0">
-        <v>10.441701070921741</v>
+        <v>10.178649297320051</v>
       </c>
       <c r="G7" s="0">
-        <v>6.4991584764207539</v>
+        <v>6.4153144309158225</v>
       </c>
       <c r="H7" s="0">
-        <v>4.6159822242897111</v>
+        <v>4.6763101517562449</v>
       </c>
       <c r="I7" s="0">
-        <v>0.77860136855019635</v>
+        <v>0.73986580082587927</v>
       </c>
       <c r="J7" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>176.99028531019502</v>
+        <v>180.94280389518167</v>
       </c>
       <c r="L7" s="0">
         <v>890</v>
       </c>
       <c r="M7" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N7" s="0">
         <v>890</v>
       </c>
       <c r="O7" s="0">
-        <v>57.526575853216087</v>
+        <v>57.403324202218769</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -521,37 +521,37 @@
         <v>4.8614133333333331</v>
       </c>
       <c r="E8" s="0">
-        <v>19.31870657314164</v>
+        <v>15.003555166653031</v>
       </c>
       <c r="F8" s="0">
-        <v>10.734938167901371</v>
+        <v>10.464499040656593</v>
       </c>
       <c r="G8" s="0">
-        <v>6.078484851965813</v>
+        <v>5.9973613066508973</v>
       </c>
       <c r="H8" s="0">
-        <v>4.9354404478441447</v>
+        <v>5.0021998785917541</v>
       </c>
       <c r="I8" s="0">
-        <v>0.82294677098138347</v>
+        <v>0.7820050109633977</v>
       </c>
       <c r="J8" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>189.18723355069983</v>
+        <v>193.23886839831297</v>
       </c>
       <c r="L8" s="0">
         <v>890</v>
       </c>
       <c r="M8" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N8" s="0">
         <v>890</v>
       </c>
       <c r="O8" s="0">
-        <v>57.554393331099241</v>
+        <v>57.434884778660482</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -571,37 +571,37 @@
         <v>5.1233760000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>21.811572645139336</v>
+        <v>16.871115234837813</v>
       </c>
       <c r="F9" s="0">
-        <v>11.020375387564757</v>
+        <v>10.742745404503058</v>
       </c>
       <c r="G9" s="0">
-        <v>5.6977519745106511</v>
+        <v>5.6189484686705393</v>
       </c>
       <c r="H9" s="0">
-        <v>5.2652344528521775</v>
+        <v>5.3390772610338768</v>
       </c>
       <c r="I9" s="0">
-        <v>0.86729217341257081</v>
+        <v>0.82414422110091623</v>
       </c>
       <c r="J9" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>202.02945664545462</v>
+        <v>206.18107437807913</v>
       </c>
       <c r="L9" s="0">
         <v>890</v>
       </c>
       <c r="M9" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N9" s="0">
         <v>890</v>
       </c>
       <c r="O9" s="0">
-        <v>57.576598096211214</v>
+        <v>57.462409841011471</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -621,37 +621,37 @@
         <v>5.3853386666666667</v>
       </c>
       <c r="E10" s="0">
-        <v>24.326775068766846</v>
+        <v>18.875025576067049</v>
       </c>
       <c r="F10" s="0">
-        <v>11.298603891500067</v>
+        <v>11.013964657653499</v>
       </c>
       <c r="G10" s="0">
-        <v>5.3510989524191608</v>
+        <v>5.2742923148804541</v>
       </c>
       <c r="H10" s="0">
-        <v>5.6063250309429238</v>
+        <v>5.6879668795300686</v>
       </c>
       <c r="I10" s="0">
-        <v>0.91163757584375782</v>
+        <v>0.86628343123843465</v>
       </c>
       <c r="J10" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>215.63794683542687</v>
+        <v>220.03442265863271</v>
       </c>
       <c r="L10" s="0">
         <v>890</v>
       </c>
       <c r="M10" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="0">
         <v>890</v>
       </c>
       <c r="O10" s="0">
-        <v>57.593210034297492</v>
+        <v>57.489092994083045</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -671,40 +671,40 @@
         <v>5.6473013333333331</v>
       </c>
       <c r="E11" s="0">
-        <v>27.134881131722675</v>
+        <v>21.01822287602354</v>
       </c>
       <c r="F11" s="0">
-        <v>11.570143737706886</v>
+        <v>11.278663756585226</v>
       </c>
       <c r="G11" s="0">
-        <v>5.0337619473924891</v>
+        <v>4.9587783842814846</v>
       </c>
       <c r="H11" s="0">
-        <v>5.9597573968590494</v>
+        <v>6.0498771421395006</v>
       </c>
       <c r="I11" s="0">
-        <v>0.95598297827494505</v>
+        <v>0.90842264137595319</v>
       </c>
       <c r="J11" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>230.24932193541821</v>
+        <v>234.75095847596126</v>
       </c>
       <c r="L11" s="0">
         <v>890</v>
       </c>
       <c r="M11" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N11" s="0">
         <v>890</v>
       </c>
       <c r="O11" s="0">
-        <v>57.610330207974869</v>
+        <v>57.514916166808305</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -721,40 +721,40 @@
         <v>5.9092640000000003</v>
       </c>
       <c r="E12" s="0">
-        <v>30.105011805261494</v>
+        <v>23.303465187357613</v>
       </c>
       <c r="F12" s="0">
-        <v>11.835455307058334</v>
+        <v>11.537291484060631</v>
       </c>
       <c r="G12" s="0">
-        <v>4.7418734511692717</v>
+        <v>4.6686793801009579</v>
       </c>
       <c r="H12" s="0">
-        <v>6.3266133752688969</v>
+        <v>6.4258000084279221</v>
       </c>
       <c r="I12" s="0">
-        <v>1.0003283807061323</v>
+        <v>0.95056185151347161</v>
       </c>
       <c r="J12" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>245.52782393748973</v>
+        <v>250.13551716567326</v>
       </c>
       <c r="L12" s="0">
         <v>890</v>
       </c>
       <c r="M12" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N12" s="0">
         <v>890</v>
       </c>
       <c r="O12" s="0">
-        <v>57.625403588221822</v>
+        <v>57.538836547472364</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -771,37 +771,37 @@
         <v>6.1712266666666666</v>
       </c>
       <c r="E13" s="0">
-        <v>33.384016233258862</v>
+        <v>25.733333970365717</v>
       </c>
       <c r="F13" s="0">
-        <v>12.094948471967653</v>
+        <v>11.79024738681283</v>
       </c>
       <c r="G13" s="0">
-        <v>4.4722201898842044</v>
+        <v>4.4006370366730874</v>
       </c>
       <c r="H13" s="0">
-        <v>6.7080775825522947</v>
+        <v>6.8171948174758379</v>
       </c>
       <c r="I13" s="0">
-        <v>1.0446737831373194</v>
+        <v>0.99270106165099015</v>
       </c>
       <c r="J13" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>261.47345284164129</v>
+        <v>266.18809872776905</v>
       </c>
       <c r="L13" s="0">
         <v>890</v>
       </c>
       <c r="M13" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N13" s="0">
         <v>890</v>
       </c>
       <c r="O13" s="0">
-        <v>57.639816714212508</v>
+        <v>57.561709471218165</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -821,37 +821,37 @@
         <v>6.433189333333333</v>
       </c>
       <c r="E14" s="0">
-        <v>36.833993917208396</v>
+        <v>28.310243372472083</v>
       </c>
       <c r="F14" s="0">
-        <v>12.348990029704051</v>
+        <v>12.037889021598245</v>
       </c>
       <c r="G14" s="0">
-        <v>4.2221081109388914</v>
+        <v>4.1519793281945265</v>
       </c>
       <c r="H14" s="0">
-        <v>7.1054551924604201</v>
+        <v>7.2254694998795657</v>
       </c>
       <c r="I14" s="0">
-        <v>1.0890191855685065</v>
+        <v>1.0348402717885083</v>
       </c>
       <c r="J14" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>278.67921552190865</v>
+        <v>283.8034731590929</v>
       </c>
       <c r="L14" s="0">
         <v>890</v>
       </c>
       <c r="M14" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14" s="0">
         <v>890</v>
       </c>
       <c r="O14" s="0">
-        <v>57.647482526514864</v>
+        <v>57.576619389056461</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -871,37 +871,37 @@
         <v>6.6951520000000002</v>
       </c>
       <c r="E15" s="0">
-        <v>40.455897887933538</v>
+        <v>31.036437701921525</v>
       </c>
       <c r="F15" s="0">
-        <v>12.597909785671094</v>
+        <v>12.280537885222468</v>
       </c>
       <c r="G15" s="0">
-        <v>3.9892329534515283</v>
+        <v>3.9204509875065572</v>
       </c>
       <c r="H15" s="0">
-        <v>7.5202427008038395</v>
+        <v>7.6521808576620609</v>
       </c>
       <c r="I15" s="0">
-        <v>1.1333645879996939</v>
+        <v>1.0769794819260272</v>
       </c>
       <c r="J15" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K15" s="0">
-        <v>297.04037086874746</v>
+        <v>302.28017769690871</v>
       </c>
       <c r="L15" s="0">
         <v>890</v>
       </c>
       <c r="M15" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N15" s="0">
         <v>890</v>
       </c>
       <c r="O15" s="0">
-        <v>57.653839319174011</v>
+        <v>57.590792833618252</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -921,37 +921,37 @@
         <v>6.9571146666666666</v>
       </c>
       <c r="E16" s="0">
-        <v>44.404812811315189</v>
+        <v>33.914000062351256</v>
       </c>
       <c r="F16" s="0">
-        <v>12.842005574756808</v>
+        <v>12.518484309390381</v>
       </c>
       <c r="G16" s="0">
-        <v>3.7717011233659097</v>
+        <v>3.704135266030208</v>
       </c>
       <c r="H16" s="0">
-        <v>7.9539706405017725</v>
+        <v>8.0990562831555462</v>
       </c>
       <c r="I16" s="0">
-        <v>1.177709990430881</v>
+        <v>1.1191186920635456</v>
       </c>
       <c r="J16" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K16" s="0">
-        <v>316.11039796500251</v>
+        <v>321.46670601895494</v>
       </c>
       <c r="L16" s="0">
         <v>890</v>
       </c>
       <c r="M16" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N16" s="0">
         <v>890</v>
       </c>
       <c r="O16" s="0">
-        <v>57.659047196298609</v>
+        <v>57.604134005930092</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -971,37 +971,37 @@
         <v>7.2190773333333329</v>
       </c>
       <c r="E17" s="0">
-        <v>48.532755123995322</v>
+        <v>37.085273770923472</v>
       </c>
       <c r="F17" s="0">
-        <v>13.081547438902719</v>
+        <v>12.751991533032083</v>
       </c>
       <c r="G17" s="0">
-        <v>3.5678602966868596</v>
+        <v>3.501392457142591</v>
       </c>
       <c r="H17" s="0">
-        <v>8.4084009757495863</v>
+        <v>8.5680198284548599</v>
       </c>
       <c r="I17" s="0">
-        <v>1.2220553928620681</v>
+        <v>1.1612579022010638</v>
       </c>
       <c r="J17" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K17" s="0">
-        <v>336.03097319907522</v>
+        <v>341.78021264219217</v>
       </c>
       <c r="L17" s="0">
         <v>890</v>
       </c>
       <c r="M17" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="0">
         <v>890</v>
       </c>
       <c r="O17" s="0">
-        <v>57.661824530348348</v>
+        <v>57.617960726536836</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1021,37 +1021,37 @@
         <v>7.4810400000000001</v>
       </c>
       <c r="E18" s="0">
-        <v>52.999925855560832</v>
+        <v>40.27356112924582</v>
       </c>
       <c r="F18" s="0">
-        <v>13.316781127976826</v>
+        <v>12.981299114980393</v>
       </c>
       <c r="G18" s="0">
-        <v>3.3762887364292511</v>
+        <v>3.310783855831934</v>
       </c>
       <c r="H18" s="0">
-        <v>8.8854959815219701</v>
+        <v>9.0612982623903715</v>
       </c>
       <c r="I18" s="0">
-        <v>1.2664007952932555</v>
+        <v>1.2033971123385825</v>
       </c>
       <c r="J18" s="0">
-        <v>0.99305555555555558</v>
+        <v>1.1818181818181817</v>
       </c>
       <c r="K18" s="0">
-        <v>357.54983235969291</v>
+        <v>363.42343608462318</v>
       </c>
       <c r="L18" s="0">
         <v>890</v>
       </c>
       <c r="M18" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18" s="0">
         <v>890</v>
       </c>
       <c r="O18" s="0">
-        <v>57.663809660776543</v>
+        <v>57.62898241574414</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:28)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 09:01)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-06 17:28</t>
+    <t>2026-10-07 09:01</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -169,22 +169,22 @@
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" customWidth="true"/>
-    <col min="2" max="2" width="9.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
-    <col min="4" max="4" width="11.5546875" customWidth="true"/>
-    <col min="5" max="5" width="11.5546875" customWidth="true"/>
-    <col min="6" max="6" width="11.5546875" customWidth="true"/>
-    <col min="7" max="7" width="13.33203125" customWidth="true"/>
-    <col min="8" max="8" width="11.5546875" customWidth="true"/>
-    <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="11.5546875" customWidth="true"/>
-    <col min="11" max="11" width="12.77734375" customWidth="true"/>
-    <col min="12" max="12" width="13.88671875" customWidth="true"/>
-    <col min="13" max="13" width="11.21875" customWidth="true"/>
-    <col min="14" max="14" width="12.88671875" customWidth="true"/>
-    <col min="15" max="15" width="13.109375" customWidth="true"/>
-    <col min="16" max="16" width="11.77734375" customWidth="true"/>
+    <col min="1" max="1" width="61.7109375" customWidth="true"/>
+    <col min="2" max="2" width="10.140625" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="14.28515625" customWidth="true"/>
+    <col min="8" max="8" width="11.7109375" customWidth="true"/>
+    <col min="9" max="9" width="12.7109375" customWidth="true"/>
+    <col min="10" max="10" width="11.7109375" customWidth="true"/>
+    <col min="11" max="11" width="13.85546875" customWidth="true"/>
+    <col min="12" max="12" width="15" customWidth="true"/>
+    <col min="13" max="13" width="12.42578125" customWidth="true"/>
+    <col min="14" max="14" width="14" customWidth="true"/>
+    <col min="15" max="15" width="14.42578125" customWidth="true"/>
+    <col min="16" max="16" width="13.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -268,40 +268,40 @@
         <v>0.02</v>
       </c>
       <c r="D3" s="0">
-        <v>3.5516000000000005</v>
+        <v>2.8914500000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>7.5952521149320988</v>
+        <v>4.8921208349005188</v>
       </c>
       <c r="F3" s="0">
-        <v>8.9443583840071384</v>
+        <v>8.0703990972743789</v>
       </c>
       <c r="G3" s="0">
-        <v>8.6563675842085974</v>
+        <v>10.853514298066353</v>
       </c>
       <c r="H3" s="0">
-        <v>3.4656568945532746</v>
+        <v>2.764081676784151</v>
       </c>
       <c r="I3" s="0">
-        <v>0.57130896027580525</v>
+        <v>0.465117494422085</v>
       </c>
       <c r="J3" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>138.54430849415479</v>
+        <v>117.30184102883979</v>
       </c>
       <c r="L3" s="0">
         <v>890</v>
       </c>
       <c r="M3" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N3" s="0">
         <v>890</v>
       </c>
       <c r="O3" s="0">
-        <v>57.402676366410553</v>
+        <v>57.416800561535069</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -315,43 +315,43 @@
         <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>0.28196266666666664</v>
+        <v>0.35237866666666673</v>
       </c>
       <c r="D4" s="0">
-        <v>3.8135626666666673</v>
+        <v>3.2238286666666669</v>
       </c>
       <c r="E4" s="0">
-        <v>8.8316229722605026</v>
+        <v>6.1393142066575948</v>
       </c>
       <c r="F4" s="0">
-        <v>9.2683539830774482</v>
+        <v>8.5216392482118657</v>
       </c>
       <c r="G4" s="0">
-        <v>7.987332385293719</v>
+        <v>9.6390823857241479</v>
       </c>
       <c r="H4" s="0">
-        <v>3.7559473617544721</v>
+        <v>3.1123294520680887</v>
       </c>
       <c r="I4" s="0">
-        <v>0.61344817041332378</v>
+        <v>0.51858379425066692</v>
       </c>
       <c r="J4" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>148.12560672156138</v>
+        <v>127.45386406100523</v>
       </c>
       <c r="L4" s="0">
         <v>890</v>
       </c>
       <c r="M4" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N4" s="0">
         <v>890</v>
       </c>
       <c r="O4" s="0">
-        <v>57.391156018114955</v>
+        <v>57.409051866592819</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -365,43 +365,43 @@
         <v>6</v>
       </c>
       <c r="C5" s="0">
-        <v>0.54392533333333326</v>
+        <v>0.68475733333333344</v>
       </c>
       <c r="D5" s="0">
-        <v>4.0755253333333341</v>
+        <v>3.5562073333333339</v>
       </c>
       <c r="E5" s="0">
-        <v>10.186853252299368</v>
+        <v>7.5051845516446569</v>
       </c>
       <c r="F5" s="0">
-        <v>9.5813999086613855</v>
+        <v>8.9501580636345572</v>
       </c>
       <c r="G5" s="0">
-        <v>7.4001080759168953</v>
+        <v>8.6437961753168136</v>
       </c>
       <c r="H5" s="0">
-        <v>4.0539948460526922</v>
+        <v>3.470697294513708</v>
       </c>
       <c r="I5" s="0">
-        <v>0.65558738055084242</v>
+        <v>0.57205009407924901</v>
       </c>
       <c r="J5" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>158.34438371943375</v>
+        <v>138.70731463902041</v>
       </c>
       <c r="L5" s="0">
         <v>890</v>
       </c>
       <c r="M5" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N5" s="0">
         <v>890</v>
       </c>
       <c r="O5" s="0">
-        <v>57.391791491056083</v>
+        <v>57.402255435017324</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -415,43 +415,43 @@
         <v>7</v>
       </c>
       <c r="C6" s="0">
-        <v>0.80588799999999983</v>
+        <v>1.017136</v>
       </c>
       <c r="D6" s="0">
-        <v>4.3374880000000005</v>
+        <v>3.8885860000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>11.664826734344313</v>
+        <v>9.0938787015657354</v>
       </c>
       <c r="F6" s="0">
-        <v>9.8845365528063667</v>
+        <v>9.3590770512599395</v>
       </c>
       <c r="G6" s="0">
-        <v>6.8799370826669959</v>
+        <v>7.8115132194766215</v>
       </c>
       <c r="H6" s="0">
-        <v>4.3605049929280097</v>
+        <v>3.8404850836327493</v>
       </c>
       <c r="I6" s="0">
-        <v>0.69772659068836074</v>
+        <v>0.62551639390783098</v>
       </c>
       <c r="J6" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>169.2928808686853</v>
+        <v>150.98701529603616</v>
       </c>
       <c r="L6" s="0">
         <v>890</v>
       </c>
       <c r="M6" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N6" s="0">
         <v>890</v>
       </c>
       <c r="O6" s="0">
-        <v>57.381228802001871</v>
+        <v>57.396286221623015</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -465,43 +465,43 @@
         <v>8</v>
       </c>
       <c r="C7" s="0">
-        <v>1.0678506666666665</v>
+        <v>1.3495146666666669</v>
       </c>
       <c r="D7" s="0">
-        <v>4.5994506666666668</v>
+        <v>4.2209646666666671</v>
       </c>
       <c r="E7" s="0">
-        <v>13.269228622237124</v>
+        <v>10.91913672411229</v>
       </c>
       <c r="F7" s="0">
-        <v>10.178649297320051</v>
+        <v>9.7508623792359117</v>
       </c>
       <c r="G7" s="0">
-        <v>6.4153144309158225</v>
+        <v>7.1037900512837444</v>
       </c>
       <c r="H7" s="0">
-        <v>4.6763101517562449</v>
+        <v>4.2230977806809795</v>
       </c>
       <c r="I7" s="0">
-        <v>0.73986580082587927</v>
+        <v>0.67898269373641296</v>
       </c>
       <c r="J7" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>180.94280389518167</v>
+        <v>164.3185169832758</v>
       </c>
       <c r="L7" s="0">
         <v>890</v>
       </c>
       <c r="M7" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N7" s="0">
         <v>890</v>
       </c>
       <c r="O7" s="0">
-        <v>57.403324202218769</v>
+        <v>57.379486187773495</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -515,43 +515,43 @@
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <v>1.3298133333333331</v>
+        <v>1.6818933333333337</v>
       </c>
       <c r="D8" s="0">
-        <v>4.8614133333333331</v>
+        <v>4.5533433333333342</v>
       </c>
       <c r="E8" s="0">
-        <v>15.003555166653031</v>
+        <v>12.88194498212364</v>
       </c>
       <c r="F8" s="0">
-        <v>10.464499040656593</v>
+        <v>10.127502704328249</v>
       </c>
       <c r="G8" s="0">
-        <v>5.9973613066508973</v>
+        <v>6.4935025128392034</v>
       </c>
       <c r="H8" s="0">
-        <v>5.0021998785917541</v>
+        <v>4.6200028321668993</v>
       </c>
       <c r="I8" s="0">
-        <v>0.7820050109633977</v>
+        <v>0.73244899356499493</v>
       </c>
       <c r="J8" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>193.23886839831297</v>
+        <v>178.84547823608125</v>
       </c>
       <c r="L8" s="0">
         <v>890</v>
       </c>
       <c r="M8" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" s="0">
         <v>890</v>
       </c>
       <c r="O8" s="0">
-        <v>57.434884778660482</v>
+        <v>57.399449280326323</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -565,43 +565,43 @@
         <v>10</v>
       </c>
       <c r="C9" s="0">
-        <v>1.5917759999999996</v>
+        <v>2.0142720000000001</v>
       </c>
       <c r="D9" s="0">
-        <v>5.1233760000000004</v>
+        <v>4.8857220000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>16.871115234837813</v>
+        <v>14.982304828059821</v>
       </c>
       <c r="F9" s="0">
-        <v>10.742745404503058</v>
+        <v>10.490629385959346</v>
       </c>
       <c r="G9" s="0">
-        <v>5.6189484686705393</v>
+        <v>5.9606946925074187</v>
       </c>
       <c r="H9" s="0">
-        <v>5.3390772610338768</v>
+        <v>5.0329704082495521</v>
       </c>
       <c r="I9" s="0">
-        <v>0.82414422110091623</v>
+        <v>0.78591529339357691</v>
       </c>
       <c r="J9" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>206.18107437807913</v>
+        <v>194.41263529173301</v>
       </c>
       <c r="L9" s="0">
         <v>890</v>
       </c>
       <c r="M9" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N9" s="0">
         <v>890</v>
       </c>
       <c r="O9" s="0">
-        <v>57.462409841011471</v>
+        <v>57.437252308967146</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -615,43 +615,43 @@
         <v>11</v>
       </c>
       <c r="C10" s="0">
-        <v>1.8537386666666662</v>
+        <v>2.3466506666666667</v>
       </c>
       <c r="D10" s="0">
-        <v>5.3853386666666667</v>
+        <v>5.2181006666666665</v>
       </c>
       <c r="E10" s="0">
-        <v>18.875025576067049</v>
+        <v>17.339960223111682</v>
       </c>
       <c r="F10" s="0">
-        <v>11.013964657653499</v>
+        <v>10.841600380060664</v>
       </c>
       <c r="G10" s="0">
-        <v>5.2742923148804541</v>
+        <v>5.4906856299955091</v>
       </c>
       <c r="H10" s="0">
-        <v>5.6879668795300686</v>
+        <v>5.4637985165478389</v>
       </c>
       <c r="I10" s="0">
-        <v>0.86628343123843465</v>
+        <v>0.83938159322215877</v>
       </c>
       <c r="J10" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>220.03442265863271</v>
+        <v>211.01998815023092</v>
       </c>
       <c r="L10" s="0">
         <v>890</v>
       </c>
       <c r="M10" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" s="0">
         <v>890</v>
       </c>
       <c r="O10" s="0">
-        <v>57.489092994083045</v>
+        <v>57.471927874929932</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -665,31 +665,31 @@
         <v>12</v>
       </c>
       <c r="C11" s="0">
-        <v>2.115701333333333</v>
+        <v>2.6790293333333337</v>
       </c>
       <c r="D11" s="0">
-        <v>5.6473013333333331</v>
+        <v>5.5504793333333336</v>
       </c>
       <c r="E11" s="0">
-        <v>21.01822287602354</v>
+        <v>19.842794231023738</v>
       </c>
       <c r="F11" s="0">
-        <v>11.278663756585226</v>
+        <v>11.181560387008126</v>
       </c>
       <c r="G11" s="0">
-        <v>4.9587783842814846</v>
+        <v>5.0722044196005616</v>
       </c>
       <c r="H11" s="0">
-        <v>6.0498771421395006</v>
+        <v>5.9145881195305838</v>
       </c>
       <c r="I11" s="0">
-        <v>0.90842264137595319</v>
+        <v>0.89284789305074075</v>
       </c>
       <c r="J11" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>234.75095847596126</v>
+        <v>229.23386974683922</v>
       </c>
       <c r="L11" s="0">
         <v>890</v>
@@ -701,10 +701,10 @@
         <v>890</v>
       </c>
       <c r="O11" s="0">
-        <v>57.514916166808305</v>
+        <v>57.503566141316945</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -715,31 +715,31 @@
         <v>13</v>
       </c>
       <c r="C12" s="0">
-        <v>2.3776639999999993</v>
+        <v>3.0114080000000003</v>
       </c>
       <c r="D12" s="0">
-        <v>5.9092640000000003</v>
+        <v>5.8828580000000006</v>
       </c>
       <c r="E12" s="0">
-        <v>23.303465187357613</v>
+        <v>22.744239454996265</v>
       </c>
       <c r="F12" s="0">
-        <v>11.537291484060631</v>
+        <v>11.511484985686559</v>
       </c>
       <c r="G12" s="0">
-        <v>4.6686793801009579</v>
+        <v>4.6968794297120802</v>
       </c>
       <c r="H12" s="0">
-        <v>6.4258000084279221</v>
+        <v>6.3872195249940678</v>
       </c>
       <c r="I12" s="0">
-        <v>0.95056185151347161</v>
+        <v>0.94631419287932295</v>
       </c>
       <c r="J12" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>250.13551716567326</v>
+        <v>248.55446931638679</v>
       </c>
       <c r="L12" s="0">
         <v>890</v>
@@ -751,10 +751,10 @@
         <v>890</v>
       </c>
       <c r="O12" s="0">
-        <v>57.538836547472364</v>
+        <v>57.537176856271856</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -765,31 +765,31 @@
         <v>14</v>
       </c>
       <c r="C13" s="0">
-        <v>2.6396266666666661</v>
+        <v>3.3437866666666674</v>
       </c>
       <c r="D13" s="0">
-        <v>6.1712266666666666</v>
+        <v>6.2152366666666676</v>
       </c>
       <c r="E13" s="0">
-        <v>25.733333970365717</v>
+        <v>25.673584261138487</v>
       </c>
       <c r="F13" s="0">
-        <v>11.79024738681283</v>
+        <v>11.832213675515876</v>
       </c>
       <c r="G13" s="0">
-        <v>4.4006370366730874</v>
+        <v>4.3575583195304795</v>
       </c>
       <c r="H13" s="0">
-        <v>6.8171948174758379</v>
+        <v>6.8845894421058391</v>
       </c>
       <c r="I13" s="0">
-        <v>0.99270106165099015</v>
+        <v>0.99978049270790492</v>
       </c>
       <c r="J13" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>266.18809872776905</v>
+        <v>268.97183841042192</v>
       </c>
       <c r="L13" s="0">
         <v>890</v>
@@ -801,7 +801,7 @@
         <v>890</v>
       </c>
       <c r="O13" s="0">
-        <v>57.561709471218165</v>
+        <v>57.56394077091597</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -815,31 +815,31 @@
         <v>15</v>
       </c>
       <c r="C14" s="0">
-        <v>2.9015893333333325</v>
+        <v>3.6761653333333335</v>
       </c>
       <c r="D14" s="0">
-        <v>6.433189333333333</v>
+        <v>6.5476153333333338</v>
       </c>
       <c r="E14" s="0">
-        <v>28.310243372472083</v>
+        <v>28.887287021498615</v>
       </c>
       <c r="F14" s="0">
-        <v>12.037889021598245</v>
+        <v>12.144475054544047</v>
       </c>
       <c r="G14" s="0">
-        <v>4.1519793281945265</v>
+        <v>4.0488292571248623</v>
       </c>
       <c r="H14" s="0">
-        <v>7.2254694998795657</v>
+        <v>7.409549302976405</v>
       </c>
       <c r="I14" s="0">
-        <v>1.0348402717885083</v>
+        <v>1.0532467925364868</v>
       </c>
       <c r="J14" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>283.8034731590929</v>
+        <v>291.78683709045873</v>
       </c>
       <c r="L14" s="0">
         <v>890</v>
@@ -851,7 +851,7 @@
         <v>890</v>
       </c>
       <c r="O14" s="0">
-        <v>57.576619389056461</v>
+        <v>57.582182299542822</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -865,31 +865,31 @@
         <v>16</v>
       </c>
       <c r="C15" s="0">
-        <v>3.1635519999999993</v>
+        <v>4.0085439999999997</v>
       </c>
       <c r="D15" s="0">
-        <v>6.6951520000000002</v>
+        <v>6.879994</v>
       </c>
       <c r="E15" s="0">
-        <v>31.036437701921525</v>
+        <v>32.394322859887048</v>
       </c>
       <c r="F15" s="0">
-        <v>12.280537885222468</v>
+        <v>12.448906306893807</v>
       </c>
       <c r="G15" s="0">
-        <v>3.9204509875065572</v>
+        <v>3.7663213509803892</v>
       </c>
       <c r="H15" s="0">
-        <v>7.6521808576620609</v>
+        <v>7.9653320055100645</v>
       </c>
       <c r="I15" s="0">
-        <v>1.0769794819260272</v>
+        <v>1.1067130923650688</v>
       </c>
       <c r="J15" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K15" s="0">
-        <v>302.28017769690871</v>
+        <v>315.74455102375941</v>
       </c>
       <c r="L15" s="0">
         <v>890</v>
@@ -901,7 +901,7 @@
         <v>890</v>
       </c>
       <c r="O15" s="0">
-        <v>57.590792833618252</v>
+        <v>57.600075865036729</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -915,43 +915,43 @@
         <v>17</v>
       </c>
       <c r="C16" s="0">
-        <v>3.4255146666666661</v>
+        <v>4.3409226666666658</v>
       </c>
       <c r="D16" s="0">
-        <v>6.9571146666666666</v>
+        <v>7.2123726666666661</v>
       </c>
       <c r="E16" s="0">
-        <v>33.914000062351256</v>
+        <v>36.203139471345601</v>
       </c>
       <c r="F16" s="0">
-        <v>12.518484309390381</v>
+        <v>12.746068496803167</v>
       </c>
       <c r="G16" s="0">
-        <v>3.704135266030208</v>
+        <v>3.5064223089015396</v>
       </c>
       <c r="H16" s="0">
-        <v>8.0990562831555462</v>
+        <v>8.5557292753473639</v>
       </c>
       <c r="I16" s="0">
-        <v>1.1191186920635456</v>
+        <v>1.1601793921936505</v>
       </c>
       <c r="J16" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K16" s="0">
-        <v>321.46670601895494</v>
+        <v>341.23606140653737</v>
       </c>
       <c r="L16" s="0">
         <v>890</v>
       </c>
       <c r="M16" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16" s="0">
         <v>890</v>
       </c>
       <c r="O16" s="0">
-        <v>57.604134005930092</v>
+        <v>57.617420552489975</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -965,31 +965,31 @@
         <v>18</v>
       </c>
       <c r="C17" s="0">
-        <v>3.6874773333333324</v>
+        <v>4.6733013333333329</v>
       </c>
       <c r="D17" s="0">
-        <v>7.2190773333333329</v>
+        <v>7.5447513333333332</v>
       </c>
       <c r="E17" s="0">
-        <v>37.085273770923472</v>
+        <v>40.321621038260908</v>
       </c>
       <c r="F17" s="0">
-        <v>12.751991533032083</v>
+        <v>13.036458722083079</v>
       </c>
       <c r="G17" s="0">
-        <v>3.501392457142591</v>
+        <v>3.2661431837085781</v>
       </c>
       <c r="H17" s="0">
-        <v>8.5680198284548599</v>
+        <v>9.1851453878810574</v>
       </c>
       <c r="I17" s="0">
-        <v>1.1612579022010638</v>
+        <v>1.2136456920222327</v>
       </c>
       <c r="J17" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K17" s="0">
-        <v>341.78021264219217</v>
+        <v>368.799945261613</v>
       </c>
       <c r="L17" s="0">
         <v>890</v>
@@ -1001,7 +1001,7 @@
         <v>890</v>
       </c>
       <c r="O17" s="0">
-        <v>57.617960726536836</v>
+        <v>57.632705342350242</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1015,43 +1015,43 @@
         <v>19</v>
       </c>
       <c r="C18" s="0">
-        <v>3.9494399999999992</v>
+        <v>5.0056799999999999</v>
       </c>
       <c r="D18" s="0">
-        <v>7.4810400000000001</v>
+        <v>7.8771300000000002</v>
       </c>
       <c r="E18" s="0">
-        <v>40.27356112924582</v>
+        <v>44.610221643020239</v>
       </c>
       <c r="F18" s="0">
-        <v>12.981299114980393</v>
+        <v>13.320519880993899</v>
       </c>
       <c r="G18" s="0">
-        <v>3.310783855831934</v>
+        <v>3.0430818716440382</v>
       </c>
       <c r="H18" s="0">
-        <v>9.0612982623903715</v>
+        <v>9.8584268400877324</v>
       </c>
       <c r="I18" s="0">
-        <v>1.2033971123385825</v>
+        <v>1.2671119918508147</v>
       </c>
       <c r="J18" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K18" s="0">
-        <v>363.42343608462318</v>
+        <v>397.56405383033138</v>
       </c>
       <c r="L18" s="0">
         <v>890</v>
       </c>
       <c r="M18" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" s="0">
         <v>890</v>
       </c>
       <c r="O18" s="0">
-        <v>57.62898241574414</v>
+        <v>57.643311063289254</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 09:01)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 11:10)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-07 09:01</t>
+    <t>2026-10-07 11:10</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -169,22 +169,22 @@
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="61.7109375" customWidth="true"/>
-    <col min="2" max="2" width="10.140625" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" customWidth="true"/>
-    <col min="4" max="4" width="11.7109375" customWidth="true"/>
-    <col min="5" max="5" width="11.7109375" customWidth="true"/>
-    <col min="6" max="6" width="11.7109375" customWidth="true"/>
-    <col min="7" max="7" width="14.28515625" customWidth="true"/>
-    <col min="8" max="8" width="11.7109375" customWidth="true"/>
-    <col min="9" max="9" width="12.7109375" customWidth="true"/>
-    <col min="10" max="10" width="11.7109375" customWidth="true"/>
-    <col min="11" max="11" width="13.85546875" customWidth="true"/>
-    <col min="12" max="12" width="15" customWidth="true"/>
-    <col min="13" max="13" width="12.42578125" customWidth="true"/>
-    <col min="14" max="14" width="14" customWidth="true"/>
-    <col min="15" max="15" width="14.42578125" customWidth="true"/>
-    <col min="16" max="16" width="13.140625" customWidth="true"/>
+    <col min="1" max="1" width="57.44140625" customWidth="true"/>
+    <col min="2" max="2" width="9.5546875" customWidth="true"/>
+    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+    <col min="4" max="4" width="11.5546875" customWidth="true"/>
+    <col min="5" max="5" width="11.5546875" customWidth="true"/>
+    <col min="6" max="6" width="11.5546875" customWidth="true"/>
+    <col min="7" max="7" width="13.33203125" customWidth="true"/>
+    <col min="8" max="8" width="11.5546875" customWidth="true"/>
+    <col min="9" max="9" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="11.5546875" customWidth="true"/>
+    <col min="11" max="11" width="12.77734375" customWidth="true"/>
+    <col min="12" max="12" width="13.88671875" customWidth="true"/>
+    <col min="13" max="13" width="11.21875" customWidth="true"/>
+    <col min="14" max="14" width="12.88671875" customWidth="true"/>
+    <col min="15" max="15" width="13.109375" customWidth="true"/>
+    <col min="16" max="16" width="11.77734375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 11:10)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 11:55)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-07 11:10</t>
+    <t>2026-10-07 11:55</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -271,25 +271,25 @@
         <v>2.8914500000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>4.8921208349005188</v>
+        <v>4.8882878760403408</v>
       </c>
       <c r="F3" s="0">
-        <v>8.0703990972743789</v>
+        <v>8.0362995883805244</v>
       </c>
       <c r="G3" s="0">
-        <v>10.853514298066353</v>
+        <v>10.669785081983333</v>
       </c>
       <c r="H3" s="0">
-        <v>2.764081676784151</v>
+        <v>2.8116780018987511</v>
       </c>
       <c r="I3" s="0">
-        <v>0.465117494422085</v>
+        <v>0.46119531633083594</v>
       </c>
       <c r="J3" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>117.30184102883979</v>
+        <v>122.57596489978596</v>
       </c>
       <c r="L3" s="0">
         <v>890</v>
@@ -301,7 +301,7 @@
         <v>890</v>
       </c>
       <c r="O3" s="0">
-        <v>57.416800561535069</v>
+        <v>57.456242054841276</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -321,25 +321,25 @@
         <v>3.2238286666666669</v>
       </c>
       <c r="E4" s="0">
-        <v>6.1393142066575948</v>
+        <v>6.1339012476117096</v>
       </c>
       <c r="F4" s="0">
-        <v>8.5216392482118657</v>
+        <v>8.485633133789003</v>
       </c>
       <c r="G4" s="0">
-        <v>9.6390823857241479</v>
+        <v>9.4705696137137228</v>
       </c>
       <c r="H4" s="0">
-        <v>3.1123294520680887</v>
+        <v>3.1677080918722069</v>
       </c>
       <c r="I4" s="0">
-        <v>0.51858379425066692</v>
+        <v>0.51421075298543995</v>
       </c>
       <c r="J4" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>127.45386406100523</v>
+        <v>133.03792715444246</v>
       </c>
       <c r="L4" s="0">
         <v>890</v>
@@ -351,7 +351,7 @@
         <v>890</v>
       </c>
       <c r="O4" s="0">
-        <v>57.409051866592819</v>
+        <v>57.44813619200842</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -371,37 +371,37 @@
         <v>3.5562073333333339</v>
       </c>
       <c r="E5" s="0">
-        <v>7.5051845516446569</v>
+        <v>7.4978582241706961</v>
       </c>
       <c r="F5" s="0">
-        <v>8.9501580636345572</v>
+        <v>8.9123413471607211</v>
       </c>
       <c r="G5" s="0">
-        <v>8.6437961753168136</v>
+        <v>8.4873795059648209</v>
       </c>
       <c r="H5" s="0">
-        <v>3.470697294513708</v>
+        <v>3.5346599004930068</v>
       </c>
       <c r="I5" s="0">
-        <v>0.57205009407924901</v>
+        <v>0.56722618964004401</v>
       </c>
       <c r="J5" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>138.70731463902041</v>
+        <v>144.54536606381507</v>
       </c>
       <c r="L5" s="0">
         <v>890</v>
       </c>
       <c r="M5" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N5" s="0">
         <v>890</v>
       </c>
       <c r="O5" s="0">
-        <v>57.402255435017324</v>
+        <v>57.441004772869711</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -421,37 +421,37 @@
         <v>3.8885860000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>9.0938787015657354</v>
+        <v>9.0840595240437221</v>
       </c>
       <c r="F6" s="0">
-        <v>9.3590770512599395</v>
+        <v>9.3195325470413693</v>
       </c>
       <c r="G6" s="0">
-        <v>7.8115132194766215</v>
+        <v>7.6648924365960332</v>
       </c>
       <c r="H6" s="0">
-        <v>3.8404850836327493</v>
+        <v>3.9139492495374082</v>
       </c>
       <c r="I6" s="0">
-        <v>0.62551639390783098</v>
+        <v>0.62024162629464807</v>
       </c>
       <c r="J6" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>150.98701529603616</v>
+        <v>157.09828162790376</v>
       </c>
       <c r="L6" s="0">
         <v>890</v>
       </c>
       <c r="M6" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6" s="0">
         <v>890</v>
       </c>
       <c r="O6" s="0">
-        <v>57.396286221623015</v>
+        <v>57.434668608534317</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -471,37 +471,37 @@
         <v>4.2209646666666671</v>
       </c>
       <c r="E7" s="0">
-        <v>10.91913672411229</v>
+        <v>10.798794948313823</v>
       </c>
       <c r="F7" s="0">
-        <v>9.7508623792359117</v>
+        <v>9.7096624813850347</v>
       </c>
       <c r="G7" s="0">
-        <v>7.1037900512837444</v>
+        <v>6.9652038994856031</v>
       </c>
       <c r="H7" s="0">
-        <v>4.2230977806809795</v>
+        <v>4.3071244478881043</v>
       </c>
       <c r="I7" s="0">
-        <v>0.67898269373641296</v>
+        <v>0.67325706294925203</v>
       </c>
       <c r="J7" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>164.3185169832758</v>
+        <v>170.80924485532194</v>
       </c>
       <c r="L7" s="0">
         <v>890</v>
       </c>
       <c r="M7" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N7" s="0">
         <v>890</v>
       </c>
       <c r="O7" s="0">
-        <v>57.379486187773495</v>
+        <v>57.417294292424657</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -521,25 +521,25 @@
         <v>4.5533433333333342</v>
       </c>
       <c r="E8" s="0">
-        <v>12.88194498212364</v>
+        <v>12.753747583979612</v>
       </c>
       <c r="F8" s="0">
-        <v>10.127502704328249</v>
+        <v>10.084711404371916</v>
       </c>
       <c r="G8" s="0">
-        <v>6.4935025128392034</v>
+        <v>6.3615816512669943</v>
       </c>
       <c r="H8" s="0">
-        <v>4.6200028321668993</v>
+        <v>4.7158083703956075</v>
       </c>
       <c r="I8" s="0">
-        <v>0.73244899356499493</v>
+        <v>0.72627249960385609</v>
       </c>
       <c r="J8" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>178.84547823608125</v>
+        <v>185.65210942737741</v>
       </c>
       <c r="L8" s="0">
         <v>890</v>
@@ -551,7 +551,7 @@
         <v>890</v>
       </c>
       <c r="O8" s="0">
-        <v>57.399449280326323</v>
+        <v>57.412303017340065</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -571,25 +571,25 @@
         <v>4.8857220000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>14.982304828059821</v>
+        <v>14.961253825654682</v>
       </c>
       <c r="F9" s="0">
-        <v>10.490629385959346</v>
+        <v>10.446303782511869</v>
       </c>
       <c r="G9" s="0">
-        <v>5.9606946925074187</v>
+        <v>5.8343497390674512</v>
       </c>
       <c r="H9" s="0">
-        <v>5.0329704082495521</v>
+        <v>5.141961202482717</v>
       </c>
       <c r="I9" s="0">
-        <v>0.78591529339357691</v>
+        <v>0.77928793625846005</v>
       </c>
       <c r="J9" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>194.41263529173301</v>
+        <v>201.55465764814781</v>
       </c>
       <c r="L9" s="0">
         <v>890</v>
@@ -601,7 +601,7 @@
         <v>890</v>
       </c>
       <c r="O9" s="0">
-        <v>57.437252308967146</v>
+        <v>57.434420568672842</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -621,25 +621,25 @@
         <v>5.2181006666666665</v>
       </c>
       <c r="E10" s="0">
-        <v>17.339960223111682</v>
+        <v>17.313637121415429</v>
       </c>
       <c r="F10" s="0">
-        <v>10.841600380060664</v>
+        <v>10.795791834023781</v>
       </c>
       <c r="G10" s="0">
-        <v>5.4906856299955091</v>
+        <v>5.3690069483424532</v>
       </c>
       <c r="H10" s="0">
-        <v>5.4637985165478389</v>
+        <v>5.5876254749980818</v>
       </c>
       <c r="I10" s="0">
-        <v>0.83938159322215877</v>
+        <v>0.832303372913064</v>
       </c>
       <c r="J10" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>211.01998815023092</v>
+        <v>218.73947369418769</v>
       </c>
       <c r="L10" s="0">
         <v>890</v>
@@ -651,7 +651,7 @@
         <v>890</v>
       </c>
       <c r="O10" s="0">
-        <v>57.471927874929932</v>
+        <v>57.468769512643362</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -671,25 +671,25 @@
         <v>5.5504793333333336</v>
       </c>
       <c r="E11" s="0">
-        <v>19.842794231023738</v>
+        <v>19.81048371773349</v>
       </c>
       <c r="F11" s="0">
-        <v>11.181560387008126</v>
+        <v>11.134315422630499</v>
       </c>
       <c r="G11" s="0">
-        <v>5.0722044196005616</v>
+        <v>4.9545009091275842</v>
       </c>
       <c r="H11" s="0">
-        <v>5.9145881195305838</v>
+        <v>6.055100311866239</v>
       </c>
       <c r="I11" s="0">
-        <v>0.89284789305074075</v>
+        <v>0.88531880956766806</v>
       </c>
       <c r="J11" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>229.23386974683922</v>
+        <v>237.37169621149423</v>
       </c>
       <c r="L11" s="0">
         <v>890</v>
@@ -701,7 +701,7 @@
         <v>890</v>
       </c>
       <c r="O11" s="0">
-        <v>57.503566141316945</v>
+        <v>57.500120263606924</v>
       </c>
       <c r="P11" s="0" t="s">
         <v>35</v>
@@ -721,25 +721,25 @@
         <v>5.8828580000000006</v>
       </c>
       <c r="E12" s="0">
-        <v>22.744239454996265</v>
+        <v>22.577827490730073</v>
       </c>
       <c r="F12" s="0">
-        <v>11.511484985686559</v>
+        <v>11.462846005145503</v>
       </c>
       <c r="G12" s="0">
-        <v>4.6968794297120802</v>
+        <v>4.5822753363091042</v>
       </c>
       <c r="H12" s="0">
-        <v>6.3872195249940678</v>
+        <v>6.5469658189863749</v>
       </c>
       <c r="I12" s="0">
-        <v>0.94631419287932295</v>
+        <v>0.93833424622227224</v>
       </c>
       <c r="J12" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>248.55446931638679</v>
+        <v>257.09948826028983</v>
       </c>
       <c r="L12" s="0">
         <v>890</v>
@@ -751,7 +751,7 @@
         <v>890</v>
       </c>
       <c r="O12" s="0">
-        <v>57.537176856271856</v>
+        <v>57.531081735380937</v>
       </c>
       <c r="P12" s="0" t="s">
         <v>35</v>
@@ -771,25 +771,25 @@
         <v>6.2152366666666676</v>
       </c>
       <c r="E13" s="0">
-        <v>25.673584261138487</v>
+        <v>25.625598131486321</v>
       </c>
       <c r="F13" s="0">
-        <v>11.832213675515876</v>
+        <v>11.782219533888044</v>
       </c>
       <c r="G13" s="0">
-        <v>4.3575583195304795</v>
+        <v>4.2455660846968471</v>
       </c>
       <c r="H13" s="0">
-        <v>6.8845894421058391</v>
+        <v>7.0661955088003623</v>
       </c>
       <c r="I13" s="0">
-        <v>0.99978049270790492</v>
+        <v>0.9913496828768763</v>
       </c>
       <c r="J13" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>268.97183841042192</v>
+        <v>278.50563468870985</v>
       </c>
       <c r="L13" s="0">
         <v>890</v>
@@ -801,7 +801,7 @@
         <v>890</v>
       </c>
       <c r="O13" s="0">
-        <v>57.56394077091597</v>
+        <v>57.560759008384835</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -821,37 +821,37 @@
         <v>6.5476153333333338</v>
       </c>
       <c r="E14" s="0">
-        <v>28.887287021498615</v>
+        <v>28.829812238955132</v>
       </c>
       <c r="F14" s="0">
-        <v>12.144475054544047</v>
+        <v>12.093161528392224</v>
       </c>
       <c r="G14" s="0">
-        <v>4.0488292571248623</v>
+        <v>3.9390334846159258</v>
       </c>
       <c r="H14" s="0">
-        <v>7.409549302976405</v>
+        <v>7.6160814872903115</v>
       </c>
       <c r="I14" s="0">
-        <v>1.0532467925364868</v>
+        <v>1.0443651195314803</v>
       </c>
       <c r="J14" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>291.78683709045873</v>
+        <v>301.79612259152077</v>
       </c>
       <c r="L14" s="0">
         <v>890</v>
       </c>
       <c r="M14" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N14" s="0">
         <v>890</v>
       </c>
       <c r="O14" s="0">
-        <v>57.582182299542822</v>
+        <v>57.579377277113501</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -871,25 +871,25 @@
         <v>6.879994</v>
       </c>
       <c r="E15" s="0">
-        <v>32.394322859887048</v>
+        <v>32.325780005511717</v>
       </c>
       <c r="F15" s="0">
-        <v>12.448906306893807</v>
+        <v>12.396306480514209</v>
       </c>
       <c r="G15" s="0">
-        <v>3.7663213509803892</v>
+        <v>3.6585509828071379</v>
       </c>
       <c r="H15" s="0">
-        <v>7.9653320055100645</v>
+        <v>8.1999677306619248</v>
       </c>
       <c r="I15" s="0">
-        <v>1.1067130923650688</v>
+        <v>1.0973805561860841</v>
       </c>
       <c r="J15" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K15" s="0">
-        <v>315.74455102375941</v>
+        <v>326.25073427343898</v>
       </c>
       <c r="L15" s="0">
         <v>890</v>
@@ -901,7 +901,7 @@
         <v>890</v>
       </c>
       <c r="O15" s="0">
-        <v>57.600075865036729</v>
+        <v>57.59712306095814</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -921,25 +921,25 @@
         <v>7.2123726666666661</v>
       </c>
       <c r="E16" s="0">
-        <v>36.203139471345601</v>
+        <v>36.121774504717422</v>
       </c>
       <c r="F16" s="0">
-        <v>12.746068496803167</v>
+        <v>12.692213083851506</v>
       </c>
       <c r="G16" s="0">
-        <v>3.5064223089015396</v>
+        <v>3.4004823226699346</v>
       </c>
       <c r="H16" s="0">
-        <v>8.5557292753473639</v>
+        <v>8.822277886874911</v>
       </c>
       <c r="I16" s="0">
-        <v>1.1601793921936505</v>
+        <v>1.150395992840688</v>
       </c>
       <c r="J16" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K16" s="0">
-        <v>341.23606140653737</v>
+        <v>352.81538070273098</v>
       </c>
       <c r="L16" s="0">
         <v>890</v>
@@ -951,7 +951,7 @@
         <v>890</v>
       </c>
       <c r="O16" s="0">
-        <v>57.617420552489975</v>
+        <v>57.614401507808559</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -971,25 +971,25 @@
         <v>7.5447513333333332</v>
       </c>
       <c r="E17" s="0">
-        <v>40.321621038260908</v>
+        <v>40.22550449788875</v>
       </c>
       <c r="F17" s="0">
-        <v>13.036458722083079</v>
+        <v>12.981376335849145</v>
       </c>
       <c r="G17" s="0">
-        <v>3.2661431837085781</v>
+        <v>3.161819875277442</v>
       </c>
       <c r="H17" s="0">
-        <v>9.1851453878810574</v>
+        <v>9.4882065340194544</v>
       </c>
       <c r="I17" s="0">
-        <v>1.2136456920222327</v>
+        <v>1.2034114294952922</v>
       </c>
       <c r="J17" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K17" s="0">
-        <v>368.799945261613</v>
+        <v>380.94614159895355</v>
       </c>
       <c r="L17" s="0">
         <v>890</v>
@@ -1001,7 +1001,7 @@
         <v>890</v>
       </c>
       <c r="O17" s="0">
-        <v>57.632705342350242</v>
+        <v>57.62963781493356</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1021,25 +1021,25 @@
         <v>7.8771300000000002</v>
       </c>
       <c r="E18" s="0">
-        <v>44.610221643020239</v>
+        <v>44.497953930116552</v>
       </c>
       <c r="F18" s="0">
-        <v>13.320519880993899</v>
+        <v>13.264237263408589</v>
       </c>
       <c r="G18" s="0">
-        <v>3.0430818716440382</v>
+        <v>2.9401486064048905</v>
       </c>
       <c r="H18" s="0">
-        <v>9.8584268400877324</v>
+        <v>10.203565879169263</v>
       </c>
       <c r="I18" s="0">
-        <v>1.2671119918508147</v>
+        <v>1.2564268661498963</v>
       </c>
       <c r="J18" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K18" s="0">
-        <v>397.56405383033138</v>
+        <v>410.49503205984513</v>
       </c>
       <c r="L18" s="0">
         <v>890</v>
@@ -1051,7 +1051,7 @@
         <v>890</v>
       </c>
       <c r="O18" s="0">
-        <v>57.643311063289254</v>
+        <v>57.641528196894342</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 11:55)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 15:03)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-07 11:55</t>
+    <t>2026-10-07 15:03</t>
   </si>
   <si>
     <t>Iteration</t>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 15:03)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-06 17:28)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-07 15:03</t>
+    <t>2026-10-06 17:28</t>
   </si>
   <si>
     <t>Iteration</t>
@@ -268,40 +268,40 @@
         <v>0.02</v>
       </c>
       <c r="D3" s="0">
-        <v>2.8914500000000003</v>
+        <v>3.5516000000000005</v>
       </c>
       <c r="E3" s="0">
-        <v>4.8882878760403408</v>
+        <v>7.5952521149320988</v>
       </c>
       <c r="F3" s="0">
-        <v>8.0362995883805244</v>
+        <v>8.9443583840071384</v>
       </c>
       <c r="G3" s="0">
-        <v>10.669785081983333</v>
+        <v>8.6563675842085974</v>
       </c>
       <c r="H3" s="0">
-        <v>2.8116780018987511</v>
+        <v>3.4656568945532746</v>
       </c>
       <c r="I3" s="0">
-        <v>0.46119531633083594</v>
+        <v>0.57130896027580525</v>
       </c>
       <c r="J3" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K3" s="0">
-        <v>122.57596489978596</v>
+        <v>138.54430849415479</v>
       </c>
       <c r="L3" s="0">
         <v>890</v>
       </c>
       <c r="M3" s="0">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N3" s="0">
         <v>890</v>
       </c>
       <c r="O3" s="0">
-        <v>57.456242054841276</v>
+        <v>57.402676366410553</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>34</v>
@@ -315,43 +315,43 @@
         <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>0.35237866666666673</v>
+        <v>0.28196266666666664</v>
       </c>
       <c r="D4" s="0">
-        <v>3.2238286666666669</v>
+        <v>3.8135626666666673</v>
       </c>
       <c r="E4" s="0">
-        <v>6.1339012476117096</v>
+        <v>8.8316229722605026</v>
       </c>
       <c r="F4" s="0">
-        <v>8.485633133789003</v>
+        <v>9.2683539830774482</v>
       </c>
       <c r="G4" s="0">
-        <v>9.4705696137137228</v>
+        <v>7.987332385293719</v>
       </c>
       <c r="H4" s="0">
-        <v>3.1677080918722069</v>
+        <v>3.7559473617544721</v>
       </c>
       <c r="I4" s="0">
-        <v>0.51421075298543995</v>
+        <v>0.61344817041332378</v>
       </c>
       <c r="J4" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K4" s="0">
-        <v>133.03792715444246</v>
+        <v>148.12560672156138</v>
       </c>
       <c r="L4" s="0">
         <v>890</v>
       </c>
       <c r="M4" s="0">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N4" s="0">
         <v>890</v>
       </c>
       <c r="O4" s="0">
-        <v>57.44813619200842</v>
+        <v>57.391156018114955</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>34</v>
@@ -365,43 +365,43 @@
         <v>6</v>
       </c>
       <c r="C5" s="0">
-        <v>0.68475733333333344</v>
+        <v>0.54392533333333326</v>
       </c>
       <c r="D5" s="0">
-        <v>3.5562073333333339</v>
+        <v>4.0755253333333341</v>
       </c>
       <c r="E5" s="0">
-        <v>7.4978582241706961</v>
+        <v>10.186853252299368</v>
       </c>
       <c r="F5" s="0">
-        <v>8.9123413471607211</v>
+        <v>9.5813999086613855</v>
       </c>
       <c r="G5" s="0">
-        <v>8.4873795059648209</v>
+        <v>7.4001080759168953</v>
       </c>
       <c r="H5" s="0">
-        <v>3.5346599004930068</v>
+        <v>4.0539948460526922</v>
       </c>
       <c r="I5" s="0">
-        <v>0.56722618964004401</v>
+        <v>0.65558738055084242</v>
       </c>
       <c r="J5" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K5" s="0">
-        <v>144.54536606381507</v>
+        <v>158.34438371943375</v>
       </c>
       <c r="L5" s="0">
         <v>890</v>
       </c>
       <c r="M5" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5" s="0">
         <v>890</v>
       </c>
       <c r="O5" s="0">
-        <v>57.441004772869711</v>
+        <v>57.391791491056083</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>34</v>
@@ -415,43 +415,43 @@
         <v>7</v>
       </c>
       <c r="C6" s="0">
-        <v>1.017136</v>
+        <v>0.80588799999999983</v>
       </c>
       <c r="D6" s="0">
-        <v>3.8885860000000001</v>
+        <v>4.3374880000000005</v>
       </c>
       <c r="E6" s="0">
-        <v>9.0840595240437221</v>
+        <v>11.664826734344313</v>
       </c>
       <c r="F6" s="0">
-        <v>9.3195325470413693</v>
+        <v>9.8845365528063667</v>
       </c>
       <c r="G6" s="0">
-        <v>7.6648924365960332</v>
+        <v>6.8799370826669959</v>
       </c>
       <c r="H6" s="0">
-        <v>3.9139492495374082</v>
+        <v>4.3605049929280097</v>
       </c>
       <c r="I6" s="0">
-        <v>0.62024162629464807</v>
+        <v>0.69772659068836074</v>
       </c>
       <c r="J6" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K6" s="0">
-        <v>157.09828162790376</v>
+        <v>169.2928808686853</v>
       </c>
       <c r="L6" s="0">
         <v>890</v>
       </c>
       <c r="M6" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N6" s="0">
         <v>890</v>
       </c>
       <c r="O6" s="0">
-        <v>57.434668608534317</v>
+        <v>57.381228802001871</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>34</v>
@@ -465,31 +465,31 @@
         <v>8</v>
       </c>
       <c r="C7" s="0">
-        <v>1.3495146666666669</v>
+        <v>1.0678506666666665</v>
       </c>
       <c r="D7" s="0">
-        <v>4.2209646666666671</v>
+        <v>4.5994506666666668</v>
       </c>
       <c r="E7" s="0">
-        <v>10.798794948313823</v>
+        <v>13.269228622237124</v>
       </c>
       <c r="F7" s="0">
-        <v>9.7096624813850347</v>
+        <v>10.178649297320051</v>
       </c>
       <c r="G7" s="0">
-        <v>6.9652038994856031</v>
+        <v>6.4153144309158225</v>
       </c>
       <c r="H7" s="0">
-        <v>4.3071244478881043</v>
+        <v>4.6763101517562449</v>
       </c>
       <c r="I7" s="0">
-        <v>0.67325706294925203</v>
+        <v>0.73986580082587927</v>
       </c>
       <c r="J7" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K7" s="0">
-        <v>170.80924485532194</v>
+        <v>180.94280389518167</v>
       </c>
       <c r="L7" s="0">
         <v>890</v>
@@ -501,7 +501,7 @@
         <v>890</v>
       </c>
       <c r="O7" s="0">
-        <v>57.417294292424657</v>
+        <v>57.403324202218769</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>34</v>
@@ -515,43 +515,43 @@
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <v>1.6818933333333337</v>
+        <v>1.3298133333333331</v>
       </c>
       <c r="D8" s="0">
-        <v>4.5533433333333342</v>
+        <v>4.8614133333333331</v>
       </c>
       <c r="E8" s="0">
-        <v>12.753747583979612</v>
+        <v>15.003555166653031</v>
       </c>
       <c r="F8" s="0">
-        <v>10.084711404371916</v>
+        <v>10.464499040656593</v>
       </c>
       <c r="G8" s="0">
-        <v>6.3615816512669943</v>
+        <v>5.9973613066508973</v>
       </c>
       <c r="H8" s="0">
-        <v>4.7158083703956075</v>
+        <v>5.0021998785917541</v>
       </c>
       <c r="I8" s="0">
-        <v>0.72627249960385609</v>
+        <v>0.7820050109633977</v>
       </c>
       <c r="J8" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K8" s="0">
-        <v>185.65210942737741</v>
+        <v>193.23886839831297</v>
       </c>
       <c r="L8" s="0">
         <v>890</v>
       </c>
       <c r="M8" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N8" s="0">
         <v>890</v>
       </c>
       <c r="O8" s="0">
-        <v>57.412303017340065</v>
+        <v>57.434884778660482</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>34</v>
@@ -565,43 +565,43 @@
         <v>10</v>
       </c>
       <c r="C9" s="0">
-        <v>2.0142720000000001</v>
+        <v>1.5917759999999996</v>
       </c>
       <c r="D9" s="0">
-        <v>4.8857220000000004</v>
+        <v>5.1233760000000004</v>
       </c>
       <c r="E9" s="0">
-        <v>14.961253825654682</v>
+        <v>16.871115234837813</v>
       </c>
       <c r="F9" s="0">
-        <v>10.446303782511869</v>
+        <v>10.742745404503058</v>
       </c>
       <c r="G9" s="0">
-        <v>5.8343497390674512</v>
+        <v>5.6189484686705393</v>
       </c>
       <c r="H9" s="0">
-        <v>5.141961202482717</v>
+        <v>5.3390772610338768</v>
       </c>
       <c r="I9" s="0">
-        <v>0.77928793625846005</v>
+        <v>0.82414422110091623</v>
       </c>
       <c r="J9" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K9" s="0">
-        <v>201.55465764814781</v>
+        <v>206.18107437807913</v>
       </c>
       <c r="L9" s="0">
         <v>890</v>
       </c>
       <c r="M9" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N9" s="0">
         <v>890</v>
       </c>
       <c r="O9" s="0">
-        <v>57.434420568672842</v>
+        <v>57.462409841011471</v>
       </c>
       <c r="P9" s="0" t="s">
         <v>34</v>
@@ -615,43 +615,43 @@
         <v>11</v>
       </c>
       <c r="C10" s="0">
-        <v>2.3466506666666667</v>
+        <v>1.8537386666666662</v>
       </c>
       <c r="D10" s="0">
-        <v>5.2181006666666665</v>
+        <v>5.3853386666666667</v>
       </c>
       <c r="E10" s="0">
-        <v>17.313637121415429</v>
+        <v>18.875025576067049</v>
       </c>
       <c r="F10" s="0">
-        <v>10.795791834023781</v>
+        <v>11.013964657653499</v>
       </c>
       <c r="G10" s="0">
-        <v>5.3690069483424532</v>
+        <v>5.2742923148804541</v>
       </c>
       <c r="H10" s="0">
-        <v>5.5876254749980818</v>
+        <v>5.6879668795300686</v>
       </c>
       <c r="I10" s="0">
-        <v>0.832303372913064</v>
+        <v>0.86628343123843465</v>
       </c>
       <c r="J10" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K10" s="0">
-        <v>218.73947369418769</v>
+        <v>220.03442265863271</v>
       </c>
       <c r="L10" s="0">
         <v>890</v>
       </c>
       <c r="M10" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N10" s="0">
         <v>890</v>
       </c>
       <c r="O10" s="0">
-        <v>57.468769512643362</v>
+        <v>57.489092994083045</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>34</v>
@@ -665,31 +665,31 @@
         <v>12</v>
       </c>
       <c r="C11" s="0">
-        <v>2.6790293333333337</v>
+        <v>2.115701333333333</v>
       </c>
       <c r="D11" s="0">
-        <v>5.5504793333333336</v>
+        <v>5.6473013333333331</v>
       </c>
       <c r="E11" s="0">
-        <v>19.81048371773349</v>
+        <v>21.01822287602354</v>
       </c>
       <c r="F11" s="0">
-        <v>11.134315422630499</v>
+        <v>11.278663756585226</v>
       </c>
       <c r="G11" s="0">
-        <v>4.9545009091275842</v>
+        <v>4.9587783842814846</v>
       </c>
       <c r="H11" s="0">
-        <v>6.055100311866239</v>
+        <v>6.0498771421395006</v>
       </c>
       <c r="I11" s="0">
-        <v>0.88531880956766806</v>
+        <v>0.90842264137595319</v>
       </c>
       <c r="J11" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K11" s="0">
-        <v>237.37169621149423</v>
+        <v>234.75095847596126</v>
       </c>
       <c r="L11" s="0">
         <v>890</v>
@@ -701,10 +701,10 @@
         <v>890</v>
       </c>
       <c r="O11" s="0">
-        <v>57.500120263606924</v>
+        <v>57.514916166808305</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -715,31 +715,31 @@
         <v>13</v>
       </c>
       <c r="C12" s="0">
-        <v>3.0114080000000003</v>
+        <v>2.3776639999999993</v>
       </c>
       <c r="D12" s="0">
-        <v>5.8828580000000006</v>
+        <v>5.9092640000000003</v>
       </c>
       <c r="E12" s="0">
-        <v>22.577827490730073</v>
+        <v>23.303465187357613</v>
       </c>
       <c r="F12" s="0">
-        <v>11.462846005145503</v>
+        <v>11.537291484060631</v>
       </c>
       <c r="G12" s="0">
-        <v>4.5822753363091042</v>
+        <v>4.6686793801009579</v>
       </c>
       <c r="H12" s="0">
-        <v>6.5469658189863749</v>
+        <v>6.4258000084279221</v>
       </c>
       <c r="I12" s="0">
-        <v>0.93833424622227224</v>
+        <v>0.95056185151347161</v>
       </c>
       <c r="J12" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K12" s="0">
-        <v>257.09948826028983</v>
+        <v>250.13551716567326</v>
       </c>
       <c r="L12" s="0">
         <v>890</v>
@@ -751,10 +751,10 @@
         <v>890</v>
       </c>
       <c r="O12" s="0">
-        <v>57.531081735380937</v>
+        <v>57.538836547472364</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -765,31 +765,31 @@
         <v>14</v>
       </c>
       <c r="C13" s="0">
-        <v>3.3437866666666674</v>
+        <v>2.6396266666666661</v>
       </c>
       <c r="D13" s="0">
-        <v>6.2152366666666676</v>
+        <v>6.1712266666666666</v>
       </c>
       <c r="E13" s="0">
-        <v>25.625598131486321</v>
+        <v>25.733333970365717</v>
       </c>
       <c r="F13" s="0">
-        <v>11.782219533888044</v>
+        <v>11.79024738681283</v>
       </c>
       <c r="G13" s="0">
-        <v>4.2455660846968471</v>
+        <v>4.4006370366730874</v>
       </c>
       <c r="H13" s="0">
-        <v>7.0661955088003623</v>
+        <v>6.8171948174758379</v>
       </c>
       <c r="I13" s="0">
-        <v>0.9913496828768763</v>
+        <v>0.99270106165099015</v>
       </c>
       <c r="J13" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K13" s="0">
-        <v>278.50563468870985</v>
+        <v>266.18809872776905</v>
       </c>
       <c r="L13" s="0">
         <v>890</v>
@@ -801,7 +801,7 @@
         <v>890</v>
       </c>
       <c r="O13" s="0">
-        <v>57.560759008384835</v>
+        <v>57.561709471218165</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>35</v>
@@ -815,43 +815,43 @@
         <v>15</v>
       </c>
       <c r="C14" s="0">
-        <v>3.6761653333333335</v>
+        <v>2.9015893333333325</v>
       </c>
       <c r="D14" s="0">
-        <v>6.5476153333333338</v>
+        <v>6.433189333333333</v>
       </c>
       <c r="E14" s="0">
-        <v>28.829812238955132</v>
+        <v>28.310243372472083</v>
       </c>
       <c r="F14" s="0">
-        <v>12.093161528392224</v>
+        <v>12.037889021598245</v>
       </c>
       <c r="G14" s="0">
-        <v>3.9390334846159258</v>
+        <v>4.1519793281945265</v>
       </c>
       <c r="H14" s="0">
-        <v>7.6160814872903115</v>
+        <v>7.2254694998795657</v>
       </c>
       <c r="I14" s="0">
-        <v>1.0443651195314803</v>
+        <v>1.0348402717885083</v>
       </c>
       <c r="J14" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K14" s="0">
-        <v>301.79612259152077</v>
+        <v>283.8034731590929</v>
       </c>
       <c r="L14" s="0">
         <v>890</v>
       </c>
       <c r="M14" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" s="0">
         <v>890</v>
       </c>
       <c r="O14" s="0">
-        <v>57.579377277113501</v>
+        <v>57.576619389056461</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>35</v>
@@ -865,31 +865,31 @@
         <v>16</v>
       </c>
       <c r="C15" s="0">
-        <v>4.0085439999999997</v>
+        <v>3.1635519999999993</v>
       </c>
       <c r="D15" s="0">
-        <v>6.879994</v>
+        <v>6.6951520000000002</v>
       </c>
       <c r="E15" s="0">
-        <v>32.325780005511717</v>
+        <v>31.036437701921525</v>
       </c>
       <c r="F15" s="0">
-        <v>12.396306480514209</v>
+        <v>12.280537885222468</v>
       </c>
       <c r="G15" s="0">
-        <v>3.6585509828071379</v>
+        <v>3.9204509875065572</v>
       </c>
       <c r="H15" s="0">
-        <v>8.1999677306619248</v>
+        <v>7.6521808576620609</v>
       </c>
       <c r="I15" s="0">
-        <v>1.0973805561860841</v>
+        <v>1.0769794819260272</v>
       </c>
       <c r="J15" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K15" s="0">
-        <v>326.25073427343898</v>
+        <v>302.28017769690871</v>
       </c>
       <c r="L15" s="0">
         <v>890</v>
@@ -901,7 +901,7 @@
         <v>890</v>
       </c>
       <c r="O15" s="0">
-        <v>57.59712306095814</v>
+        <v>57.590792833618252</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>35</v>
@@ -915,43 +915,43 @@
         <v>17</v>
       </c>
       <c r="C16" s="0">
-        <v>4.3409226666666658</v>
+        <v>3.4255146666666661</v>
       </c>
       <c r="D16" s="0">
-        <v>7.2123726666666661</v>
+        <v>6.9571146666666666</v>
       </c>
       <c r="E16" s="0">
-        <v>36.121774504717422</v>
+        <v>33.914000062351256</v>
       </c>
       <c r="F16" s="0">
-        <v>12.692213083851506</v>
+        <v>12.518484309390381</v>
       </c>
       <c r="G16" s="0">
-        <v>3.4004823226699346</v>
+        <v>3.704135266030208</v>
       </c>
       <c r="H16" s="0">
-        <v>8.822277886874911</v>
+        <v>8.0990562831555462</v>
       </c>
       <c r="I16" s="0">
-        <v>1.150395992840688</v>
+        <v>1.1191186920635456</v>
       </c>
       <c r="J16" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K16" s="0">
-        <v>352.81538070273098</v>
+        <v>321.46670601895494</v>
       </c>
       <c r="L16" s="0">
         <v>890</v>
       </c>
       <c r="M16" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16" s="0">
         <v>890</v>
       </c>
       <c r="O16" s="0">
-        <v>57.614401507808559</v>
+        <v>57.604134005930092</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>35</v>
@@ -965,31 +965,31 @@
         <v>18</v>
       </c>
       <c r="C17" s="0">
-        <v>4.6733013333333329</v>
+        <v>3.6874773333333324</v>
       </c>
       <c r="D17" s="0">
-        <v>7.5447513333333332</v>
+        <v>7.2190773333333329</v>
       </c>
       <c r="E17" s="0">
-        <v>40.22550449788875</v>
+        <v>37.085273770923472</v>
       </c>
       <c r="F17" s="0">
-        <v>12.981376335849145</v>
+        <v>12.751991533032083</v>
       </c>
       <c r="G17" s="0">
-        <v>3.161819875277442</v>
+        <v>3.501392457142591</v>
       </c>
       <c r="H17" s="0">
-        <v>9.4882065340194544</v>
+        <v>8.5680198284548599</v>
       </c>
       <c r="I17" s="0">
-        <v>1.2034114294952922</v>
+        <v>1.1612579022010638</v>
       </c>
       <c r="J17" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K17" s="0">
-        <v>380.94614159895355</v>
+        <v>341.78021264219217</v>
       </c>
       <c r="L17" s="0">
         <v>890</v>
@@ -1001,7 +1001,7 @@
         <v>890</v>
       </c>
       <c r="O17" s="0">
-        <v>57.62963781493356</v>
+        <v>57.617960726536836</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>35</v>
@@ -1015,43 +1015,43 @@
         <v>19</v>
       </c>
       <c r="C18" s="0">
-        <v>5.0056799999999999</v>
+        <v>3.9494399999999992</v>
       </c>
       <c r="D18" s="0">
-        <v>7.8771300000000002</v>
+        <v>7.4810400000000001</v>
       </c>
       <c r="E18" s="0">
-        <v>44.497953930116552</v>
+        <v>40.27356112924582</v>
       </c>
       <c r="F18" s="0">
-        <v>13.264237263408589</v>
+        <v>12.981299114980393</v>
       </c>
       <c r="G18" s="0">
-        <v>2.9401486064048905</v>
+        <v>3.310783855831934</v>
       </c>
       <c r="H18" s="0">
-        <v>10.203565879169263</v>
+        <v>9.0612982623903715</v>
       </c>
       <c r="I18" s="0">
-        <v>1.2564268661498963</v>
+        <v>1.2033971123385825</v>
       </c>
       <c r="J18" s="0">
         <v>1.1818181818181817</v>
       </c>
       <c r="K18" s="0">
-        <v>410.49503205984513</v>
+        <v>363.42343608462318</v>
       </c>
       <c r="L18" s="0">
         <v>890</v>
       </c>
       <c r="M18" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" s="0">
         <v>890</v>
       </c>
       <c r="O18" s="0">
-        <v>57.641528196894342</v>
+        <v>57.62898241574414</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>35</v>

--- a/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
+++ b/Aicraft Performance Simulation/MaxPayloadSweepLog.xlsx
@@ -15,13 +15,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="36">
   <si>
-    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 15:03)</t>
+    <t>Deliverable 8 -- Maximum Payload Sweep (last run: 2026-10-07 15:05)</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>2026-10-07 15:03</t>
+    <t>2026-10-07 15:05</t>
   </si>
   <si>
     <t>Iteration</t>
